--- a/outputs/sales_item_match_audit.xlsx
+++ b/outputs/sales_item_match_audit.xlsx
@@ -2202,92 +2202,64 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>manual_override</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.195</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>RCCT-7710TU-7</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>77 x 10 Tandem Axle Utility Trailer - No Ramp</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>RCCT</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3975.00</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0.215</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Sprocket 10 Tooth</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>MPWSR-SPROCKET-10-TOOTH</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>MPWSR</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Manual override. Added supplemental catalog row from repeated Square sales notes and stable realized selling price.</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>0.195</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Rocker for GC 160 Ex</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>14441-Z0J-000</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>MPWSR</t>
-        </is>
-      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>0.192</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>LOCKNUT 1/4"</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>2264</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Barrens</t>
-        </is>
-      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -3386,7 +3358,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>review_fuzzy</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3396,97 +3368,117 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>0.849</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.234</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+          <t>0.604</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>H2PROWP</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Tucker H2Pro WP</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>3975.00</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2869.30</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit, name contains match</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>0.849</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Bulb Changer Kit with Pole</t>
+          <t>Tucker H2Pro WP</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>48450</t>
+          <t>H2PROWP</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit, name contains match</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>0.604</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Bucket Super Handle Ettore</t>
+          <t>H2Pro by Tucker®</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>JRACEN-SUPER-BUCKET-HANDLE</t>
+          <t>10041-110V-SS</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>Bucket Super Caster Ettore</t>
+          <t>Tucker® Water Fed Pole - H2Pro 3-Stage Kit - w/ Hose Reel</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>85200</t>
+          <t>10041-110V-KIT-30</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -3776,109 +3768,69 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>manual_override</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.314</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>T-CART-RIVAL</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Tucker Rival RO/DI Cart</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2308.85</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1616.20</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>0.325</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>All Purpose Window Cleaning Kit</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>17050</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>0.314</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>Universal Window Cleaning Kit</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>JRACEN-UNIVERSAL-WINDOW-CLEANING-KIT</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>0.314</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>Total Glass Care Kit</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>JRACEN-TOTAL-GLASS-CARE-KIT</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
+          <t>Manual override. Sales item and SKU both point to the internal Tucker Rival RO/DI cart SKU.</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3934,109 +3886,65 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>manual_override</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.285</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>9712612</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Truck Mount Skid CRX680</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>MPWSR</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>3500.00</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1 shared tokens</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>0.306</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>The Manatee Skid BARE</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>PWF125</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>MPWSR</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>1 shared tokens</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>0.285</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>GP REEL MOUNT KIT</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>7259</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>Barrens</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>1 shared tokens</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>0.283</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>FRAME, STEEL, TRUCK MOUNT BELT DRIVE</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>85.600.238</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>2 shared tokens</t>
-        </is>
-      </c>
+          <t>Manual override. Added supplemental catalog row from stable realized sales using the same internal SKU.</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5374,109 +5282,65 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>manual_override</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.422</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L498970</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Sodium Hydroxide - 50 lb Bag</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>AZCS</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>0.443</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>SOS-50 - 1 Gallon</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>EACOCH-SOS-50-1-GALLON</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>EacoChem</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>0.422</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>Joint Sand - Platinum - 50 lb bag</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>TDJ-JOINTINGPLA</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>Trident</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>0.420</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>Joint Sand - Grey - 50 lb bag</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>TDJ-JOINTINGGRA</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Trident</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Manual override. Added supplemental catalog row from repeated realized sales using the same internal SKU.</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5532,109 +5396,69 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.361</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>TUCKER-30</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Tucker® - 30 Water Fed Pole</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>750.16</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>525.11</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>0.369</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>30" Curved Aluminum Floor Squeegee</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>55040</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>0.361</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>Master Rubber, 30" [Case 144]</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>49890</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>0.360</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>Aluminum Super Curved Floor Squeegees, 30"</t>
-        </is>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>55037</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Normalized sales item name exactly matches the catalog name.</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6554,12 +6378,12 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
+          <t>0.291</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
           <t>0.249</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>0.242</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
@@ -6574,67 +6398,67 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
+          <t>0.291</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Solar Alpha 20</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>T-20ALPHA-SOLAR</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>1 shared tokens</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
           <t>0.249</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>FLOAT VALVE ROD 1/4-20 x 8"</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>1548</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="AD50" t="inlineStr">
         <is>
           <t>Barrens</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AE50" t="inlineStr">
         <is>
           <t>1 shared tokens</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AF50" t="inlineStr">
         <is>
           <t>0.242</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AG50" t="inlineStr">
         <is>
           <t>FLOAT VALVE BRASS ROD 1/4-20 x 2"</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AH50" t="inlineStr">
         <is>
           <t>1547</t>
-        </is>
-      </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>Barrens</t>
-        </is>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>1 shared tokens</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>0.237</t>
-        </is>
-      </c>
-      <c r="AG50" t="inlineStr">
-        <is>
-          <t>14179 O-RING BUNA-N [2.4 X 20.8]</t>
-        </is>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>3736</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
@@ -7048,109 +6872,69 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>manual_override</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>0.290</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>T-CART-RIVAL</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Tucker Rival RO/DI Cart</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>2308.85</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1616.20</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>0.294</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Bucket Super Lid Ettore</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>85100</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>0.290</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>Pole Adapter Universal Ettore</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>45006</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>0.288</t>
-        </is>
-      </c>
-      <c r="AG54" t="inlineStr">
-        <is>
-          <t>Scrapemaster Handle</t>
-        </is>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>JRACEN-SCRAPEMASTER-HANDLE</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
+          <t>Manual override. Sales alias mapped to the internal Tucker Rival RO/DI cart SKU.</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7206,7 +6990,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>review_fuzzy</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -7216,97 +7000,117 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>0.824</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0.310</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
+          <t>0.682</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>T-50HM-BARE</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Tucker® - 50 HM Water Fed Pole - Bare</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1829.98</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1280.99</t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>5 shared tokens, category fit, name contains match</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>0.824</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Ettore Grip-n-Grab Tool 50 inch</t>
+          <t>Tucker® - 50 HM Water Fed Pole - Bare</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>T-50HM-BARE</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>5 shared tokens, category fit, name contains match</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>0.310</t>
+          <t>0.682</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Bulb Changer Kit with Pole</t>
+          <t>Tucker® High Modulus - 50 Water Fed Pole</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>48450</t>
+          <t>TUCKER-50HM</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>5 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.631</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>Cobweb Brush with Pole</t>
+          <t>Tucker® - 40 Water Fed Pole</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>45221</t>
+          <t>TUCKER-40</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>4 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -8777,7 +8581,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>0.270</t>
+          <t>0.294</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
@@ -8817,47 +8621,47 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
+          <t>0.294</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>1/2 hp Motor Dual Phase</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>12023</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>1 shared tokens</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
           <t>0.270</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
+      <c r="AG67" t="inlineStr">
         <is>
           <t>STARTER MOTOR FOR BE-12000ER</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
+      <c r="AH67" t="inlineStr">
         <is>
           <t>85.591.231</t>
         </is>
       </c>
-      <c r="AD67" t="inlineStr">
+      <c r="AI67" t="inlineStr">
         <is>
           <t>BE</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>1 shared tokens</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>0.248</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>Set of Battery Cables for Electric Start Machines - Motor</t>
-        </is>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>BC-10</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>MPWSR</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -11474,109 +11278,69 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>0.275</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>TUCKER-40</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Tucker® - 40 Water Fed Pole</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1050.82</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>735.57</t>
+        </is>
+      </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>0.323</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Bulb Changer Kit with Pole</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>48450</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>0.275</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>Pole Adapter Universal Ettore</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>45006</t>
-        </is>
-      </c>
-      <c r="AD87" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE87" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>0.274</t>
-        </is>
-      </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>Ettore Cobweb Duster with 9ft Pole</t>
-        </is>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>31028</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Normalized sales item name exactly matches the catalog name.</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -16126,12 +15890,12 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
+          <t>0.419</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
           <t>0.376</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>0.370</t>
         </is>
       </c>
       <c r="P122" t="inlineStr"/>
@@ -16146,67 +15910,67 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
+          <t>0.419</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Bucket On A Belt (Grey)</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>T-BOAB-GRY</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>1 shared tokens</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
           <t>0.376</t>
         </is>
       </c>
-      <c r="W122" t="inlineStr">
+      <c r="AB122" t="inlineStr">
         <is>
           <t>Bucket Super Sieve Ettore</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
+      <c r="AC122" t="inlineStr">
         <is>
           <t>85301</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="AD122" t="inlineStr">
         <is>
           <t>JRacenstein</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
+      <c r="AE122" t="inlineStr">
         <is>
           <t>1 shared tokens</t>
         </is>
       </c>
-      <c r="AA122" t="inlineStr">
+      <c r="AF122" t="inlineStr">
         <is>
           <t>0.370</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
+      <c r="AG122" t="inlineStr">
         <is>
           <t>Bucket Super Caster Ettore</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
+      <c r="AH122" t="inlineStr">
         <is>
           <t>85200</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>1 shared tokens</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>0.366</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>Bucket Super Lid Ettore</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>85100</t>
         </is>
       </c>
       <c r="AI122" t="inlineStr">
@@ -18604,12 +18368,12 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
+          <t>0.484</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
           <t>0.460</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>0.403</t>
         </is>
       </c>
       <c r="P141" t="inlineStr"/>
@@ -18624,72 +18388,72 @@
       </c>
       <c r="V141" t="inlineStr">
         <is>
+          <t>0.484</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Boost Pump 12V</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>12032BOOST</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>2 shared tokens</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
           <t>0.460</t>
         </is>
       </c>
-      <c r="W141" t="inlineStr">
+      <c r="AB141" t="inlineStr">
         <is>
           <t>6 GPM FloJet 12V Pump</t>
         </is>
       </c>
-      <c r="X141" t="inlineStr">
+      <c r="AC141" t="inlineStr">
         <is>
           <t>R8601134A</t>
         </is>
       </c>
-      <c r="Y141" t="inlineStr">
+      <c r="AD141" t="inlineStr">
         <is>
           <t>MPWSR</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
+      <c r="AE141" t="inlineStr">
         <is>
           <t>2 shared tokens</t>
         </is>
       </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>0.403</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>12V SPEED CONTROLLER</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>7258</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>Barrens</t>
-        </is>
-      </c>
-      <c r="AE141" t="inlineStr">
-        <is>
-          <t>1 shared tokens</t>
-        </is>
-      </c>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>0.457</t>
         </is>
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>12V Electric Hose Reel Motor</t>
+          <t>12v RO Booster Panel</t>
         </is>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>101316</t>
+          <t>10070-BOOST</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>MPWSR</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
@@ -20786,109 +20550,69 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>0.280</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>0.276</t>
-        </is>
-      </c>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
-      <c r="T157" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>20025/26</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>2.5 x 10" Sediment / Carbon Combo Filter</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>28.10</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>19.68</t>
+        </is>
+      </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>0.280</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>T-bar and Golden Glove Sleeve 10in Ettore</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>JRACEN-GOLDEN-GLOVE-WASHER-COMPLETE-SLE</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>0.276</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>Scraper 5in Ettore</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>46312</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>0.235</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>Blades ProPlus 06in Carbon Stl (25) Etto</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>JRACEN-PRO-CONTOUR-STEEL-REPLACEMENT-BL</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr"/>
+      <c r="W157" t="inlineStr"/>
+      <c r="X157" t="inlineStr"/>
+      <c r="Y157" t="inlineStr"/>
+      <c r="Z157" t="inlineStr"/>
+      <c r="AA157" t="inlineStr"/>
+      <c r="AB157" t="inlineStr"/>
+      <c r="AC157" t="inlineStr"/>
+      <c r="AD157" t="inlineStr"/>
+      <c r="AE157" t="inlineStr"/>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="inlineStr"/>
+      <c r="AH157" t="inlineStr"/>
+      <c r="AI157" t="inlineStr"/>
+      <c r="AJ157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -20954,12 +20678,12 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.445</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>0.417</t>
         </is>
       </c>
       <c r="P158" t="inlineStr"/>
@@ -20969,77 +20693,77 @@
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.445</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Ettore All Purpose Squeegees 16 inch</t>
+          <t>5/16" OD Tucker® Pole Hose</t>
         </is>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>17016</t>
+          <t>5/16"-OD-TUCKER®-POLE-HOSE</t>
         </is>
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>0.417</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>Ettore Grip-n-Grab Tool 16 inch</t>
+          <t>Inline Ball Valve for 5/16" Pole Tubing</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>49016</t>
+          <t>62014-BV-5/16</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AG158" t="inlineStr">
         <is>
-          <t>Ettore Channel Classic Aluminum 16 inch</t>
+          <t>1/4"M x 5/16" PTF</t>
         </is>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>62056</t>
         </is>
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
@@ -22318,12 +22042,12 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>0.337</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="P168" t="inlineStr"/>
@@ -22333,82 +22057,82 @@
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>5 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>0.337</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Large Flo Brush</t>
+          <t>Water Fed Brush | Tucker® Glide - 4 Pencil Jets - NEW XL Size w/ Loct fitting Quad</t>
         </is>
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>59080</t>
+          <t>18GL-LT-PP</t>
         </is>
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>5 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>Cleaning Clamp Brush</t>
+          <t>GLIDE Bristle Upgrade For Tucker® Alpha Solar 20" Brush</t>
         </is>
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>55170</t>
+          <t>UGK-20ALPHA-SOLAR-GL</t>
         </is>
       </c>
       <c r="AD168" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>0.322</t>
         </is>
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>Super Brush Ettore</t>
+          <t>Water Fed Brush | Tucker® Glide - 4 Pencil Jets - NEW Standard Size w/ Loct fitting Quad</t>
         </is>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
-          <t>JRACEN-SUPER-BRUSH</t>
+          <t>12GL-LT-PP</t>
         </is>
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>5 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -23340,12 +23064,12 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.586</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.343</t>
         </is>
       </c>
       <c r="P175" t="inlineStr"/>
@@ -23355,82 +23079,82 @@
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>4 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.586</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Ettore Channel Classic Brass 16 inch [Case 12]</t>
+          <t>5/16" OD Tucker® Pole Hose</t>
         </is>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>JRACEN-MASTER-BRASS-CHANNELS-WITH-RUB-9</t>
+          <t>5/16"-OD-TUCKER®-POLE-HOSE</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>4 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.343</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>Ettore Rubber Master Replacement Dozen 16 inch [Case 12]</t>
+          <t>Tucker® Water Fed Pole - H2Pro 3-Stage Kit - w/ Hose Reel</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>JRACEN-MASTER-RUBBER-16-CASE-12</t>
+          <t>10041-110V-KIT-30</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.336</t>
         </is>
       </c>
       <c r="AG175" t="inlineStr">
         <is>
-          <t>Ettore Rubber Master Replacement Gross 16 inch [Case 144]</t>
+          <t>Tucker® Water Fed Pole - Skid Mount Kit - w/ 40 Hose Reel</t>
         </is>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>10700-WALL-110-KIT-40</t>
         </is>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -25235,7 +24959,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -25275,22 +24999,22 @@
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>CABLE, BATTERY RED 6 GAUGE RED</t>
+          <t>Large Battery Box</t>
         </is>
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>85.603.040</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="AD188" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE188" t="inlineStr">
@@ -25300,22 +25024,22 @@
       </c>
       <c r="AF188" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.312</t>
         </is>
       </c>
       <c r="AG188" t="inlineStr">
         <is>
-          <t>BATTERY, 18AH FOR BE-12000ER</t>
+          <t>Battery Hold-Down</t>
         </is>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>85.591.227</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ188" t="inlineStr">
@@ -25492,17 +25216,17 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -25510,41 +25234,41 @@
           <t>0.000</t>
         </is>
       </c>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
-      <c r="R190" t="inlineStr"/>
-      <c r="S190" t="inlineStr"/>
-      <c r="T190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>12034</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Tucker® Delivery Pump</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>251.94</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>176.36</t>
+        </is>
+      </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>0.337</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>Water Spot Remover Scrub Off Ettore</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>30161</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr"/>
+      <c r="W190" t="inlineStr"/>
+      <c r="X190" t="inlineStr"/>
+      <c r="Y190" t="inlineStr"/>
+      <c r="Z190" t="inlineStr"/>
       <c r="AA190" t="inlineStr"/>
       <c r="AB190" t="inlineStr"/>
       <c r="AC190" t="inlineStr"/>
@@ -25764,84 +25488,64 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>0.284</t>
-        </is>
-      </c>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
-      <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr"/>
-      <c r="T192" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>20008</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>4in x 10in Sediment Filter</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>38.26</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>26.79</t>
+        </is>
+      </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>0.305</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>Blades 4in for HD Scraper (10) Ettore</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>20291</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA192" t="inlineStr">
-        <is>
-          <t>0.284</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>T-bar and Golden Glove Sleeve 10in Ettore</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>JRACEN-GOLDEN-GLOVE-WASHER-COMPLETE-SLE</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr"/>
+      <c r="W192" t="inlineStr"/>
+      <c r="X192" t="inlineStr"/>
+      <c r="Y192" t="inlineStr"/>
+      <c r="Z192" t="inlineStr"/>
+      <c r="AA192" t="inlineStr"/>
+      <c r="AB192" t="inlineStr"/>
+      <c r="AC192" t="inlineStr"/>
+      <c r="AD192" t="inlineStr"/>
+      <c r="AE192" t="inlineStr"/>
       <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="inlineStr"/>
       <c r="AH192" t="inlineStr"/>
@@ -26218,109 +25922,69 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>0.298</t>
-        </is>
-      </c>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
-      <c r="R195" t="inlineStr"/>
-      <c r="S195" t="inlineStr"/>
-      <c r="T195" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>20007-10</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Tucker® DI Virgin Resin - 10 Bags</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>2077.85</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>1454.50</t>
+        </is>
+      </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>0.305</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>Trash Picker replacement pin Ettore</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>49542</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>0.298</t>
-        </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>Starter Window Cleaning Kit</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>2506</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>0.294</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>Bucket Super Lid Ettore</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>85100</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr"/>
+      <c r="W195" t="inlineStr"/>
+      <c r="X195" t="inlineStr"/>
+      <c r="Y195" t="inlineStr"/>
+      <c r="Z195" t="inlineStr"/>
+      <c r="AA195" t="inlineStr"/>
+      <c r="AB195" t="inlineStr"/>
+      <c r="AC195" t="inlineStr"/>
+      <c r="AD195" t="inlineStr"/>
+      <c r="AE195" t="inlineStr"/>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="inlineStr"/>
+      <c r="AH195" t="inlineStr"/>
+      <c r="AI195" t="inlineStr"/>
+      <c r="AJ195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -26662,12 +26326,12 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.410</t>
         </is>
       </c>
       <c r="P198" t="inlineStr"/>
@@ -26677,64 +26341,84 @@
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr">
         <is>
+          <t>2 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>0.444</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Pair Of Tucker® Euro Brush Pencil Jets</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>50006-PS</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>2 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>0.410</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>Tucker® Carbon Fiber Goosenecks</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>TUCKER®-CARBON-FIBER-GOOSENECKS</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
           <t>1 shared tokens, category fit</t>
         </is>
       </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>0.366</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>Holster Dual Nylon Ettore</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>50130</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>0.410</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>Water Fed Brush│Boar Bristle - 4 Pencil Jets</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>WATER-FED-BRUSH│BOAR-BRISTLE---4-PENCIL-JETS</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
         <is>
           <t>1 shared tokens, category fit</t>
         </is>
       </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>0.293</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>Pole Pro+ Snap-In Tip Nylon Ettore</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>JRACEN-PRO-POLE-TIP</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr"/>
-      <c r="AG198" t="inlineStr"/>
-      <c r="AH198" t="inlineStr"/>
-      <c r="AI198" t="inlineStr"/>
-      <c r="AJ198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -27186,12 +26870,12 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>0.602</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.575</t>
         </is>
       </c>
       <c r="P202" t="inlineStr"/>
@@ -27201,82 +26885,82 @@
       <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>0.602</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Bucket Super Handle Ettore</t>
+          <t>Tucker® Alpha Glide - XL</t>
         </is>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>JRACEN-SUPER-BUCKET-HANDLE</t>
+          <t>T-18ALPHA-GL</t>
         </is>
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.575</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>Bucket Super Lid Ettore</t>
+          <t>Tucker® Alpha Honey Badger</t>
         </is>
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>85100</t>
+          <t>T-12ALPHA-HB-STD</t>
         </is>
       </c>
       <c r="AD202" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.553</t>
         </is>
       </c>
       <c r="AG202" t="inlineStr">
         <is>
-          <t>Cleaning Clamp Brush</t>
+          <t>Tucker® Alpha Honey Badger XL</t>
         </is>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>55170</t>
+          <t>T-18ALPHA-HB</t>
         </is>
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -28104,12 +27788,12 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>0.666</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="P209" t="inlineStr"/>
@@ -28119,82 +27803,82 @@
       <c r="T209" t="inlineStr"/>
       <c r="U209" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>0.666</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>Flo Scrub Brush</t>
+          <t>XL ALPHA BADGER Solar Brush</t>
         </is>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>59100</t>
+          <t>T-18ALPHA-HB-SOLAR</t>
         </is>
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>Flo Brush</t>
+          <t>GLIDE Bristle Upgrade For Tucker® Alpha Solar 20" Brush</t>
         </is>
       </c>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>59070</t>
+          <t>UGK-20ALPHA-SOLAR-GL</t>
         </is>
       </c>
       <c r="AD209" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
         <is>
-          <t>0.420</t>
+          <t>0.328</t>
         </is>
       </c>
       <c r="AG209" t="inlineStr">
         <is>
-          <t>Large Flo Brush</t>
+          <t>Solar Boost 27' Water-Fed Pole Kit w/ XL Alpha Badger Solar Brush</t>
         </is>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>59080</t>
+          <t>SOLAR-BOOST-COMPLETE</t>
         </is>
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -28420,12 +28104,12 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.437</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P211" t="inlineStr"/>
@@ -28435,84 +28119,44 @@
       <c r="T211" t="inlineStr"/>
       <c r="U211" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.437</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Auto Squeegee Scrubber Ettore</t>
+          <t>Alpha Scrubber Pads │ 10 Pack Replacements</t>
         </is>
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>59016</t>
+          <t>ALPHA-SCRUBBER-PADS-│-10-PACK-REPLACEMENTS</t>
         </is>
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA211" t="inlineStr">
-        <is>
-          <t>0.281</t>
-        </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>Auto Squeegee Scrubber Wood 8" Head, 25" overall</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>59020</t>
-        </is>
-      </c>
-      <c r="AD211" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE211" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF211" t="inlineStr">
-        <is>
-          <t>0.281</t>
-        </is>
-      </c>
-      <c r="AG211" t="inlineStr">
-        <is>
-          <t>Auto Squeegee Scrubber Wood 8" Head, 17" overall</t>
-        </is>
-      </c>
-      <c r="AH211" t="inlineStr">
-        <is>
-          <t>59816</t>
-        </is>
-      </c>
-      <c r="AI211" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ211" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>3 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="inlineStr"/>
+      <c r="AC211" t="inlineStr"/>
+      <c r="AD211" t="inlineStr"/>
+      <c r="AE211" t="inlineStr"/>
+      <c r="AF211" t="inlineStr"/>
+      <c r="AG211" t="inlineStr"/>
+      <c r="AH211" t="inlineStr"/>
+      <c r="AI211" t="inlineStr"/>
+      <c r="AJ211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -29012,12 +28656,12 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.517</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="P215" t="inlineStr"/>
@@ -29032,22 +28676,22 @@
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.517</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>Extend-a-Flow Pole 06ft Ettore</t>
+          <t>Union for Pole Tubing</t>
         </is>
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>59072</t>
+          <t>63014</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
@@ -29055,16 +28699,56 @@
           <t>2 shared tokens, category fit</t>
         </is>
       </c>
-      <c r="AA215" t="inlineStr"/>
-      <c r="AB215" t="inlineStr"/>
-      <c r="AC215" t="inlineStr"/>
-      <c r="AD215" t="inlineStr"/>
-      <c r="AE215" t="inlineStr"/>
-      <c r="AF215" t="inlineStr"/>
-      <c r="AG215" t="inlineStr"/>
-      <c r="AH215" t="inlineStr"/>
-      <c r="AI215" t="inlineStr"/>
-      <c r="AJ215" t="inlineStr"/>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>0.441</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>Tucker® JUNIOR Hybrid Pole</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>TUCKER-15</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>2 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>0.440</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>Tucker® - Junior Water Fed Pole - Bare</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>ECO-15-BARE</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>2 shared tokens, category fit</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -29406,12 +29090,12 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="P218" t="inlineStr"/>
@@ -29421,82 +29105,82 @@
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>Master Brass Channels with Rubber, 22" [Case 36]</t>
+          <t>Tucker® Carbon Fiber Goosenecks</t>
         </is>
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>JRACEN-MASTER-BRASS-CHANNELS-WITH-RU-14</t>
+          <t>TUCKER®-CARBON-FIBER-GOOSENECKS</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>Master Brass Channels with Rubber, 18" [Case 36]</t>
+          <t>End Cap for Tucker Carbon Fiber Pole</t>
         </is>
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>JRACEN-MASTER-BRASS-CHANNELS-WITH-RU-11</t>
+          <t>T-4BR-CF</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.358</t>
         </is>
       </c>
       <c r="AG218" t="inlineStr">
         <is>
-          <t>Master Brass Channels with Rubber, 16" [Case 36]</t>
+          <t>End Cap for 60' Tucker Carbon Fiber Pole</t>
         </is>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>JRACEN-MASTER-BRASS-CHANNELS-WITH-RU-10</t>
+          <t>T-10BR-CF</t>
         </is>
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -29826,109 +29510,69 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>0.399</t>
-        </is>
-      </c>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
-      <c r="R221" t="inlineStr"/>
-      <c r="S221" t="inlineStr"/>
-      <c r="T221" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>T-BOAB-GRY</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Bucket On A Belt (Grey)</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>14.04</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>9.83</t>
+        </is>
+      </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>0.421</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>Holster Dual Nylon Ettore</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>50130</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA221" t="inlineStr">
-        <is>
-          <t>0.399</t>
-        </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>Super Bucket, Hanging Sieve</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>85300</t>
-        </is>
-      </c>
-      <c r="AD221" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE221" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF221" t="inlineStr">
-        <is>
-          <t>0.379</t>
-        </is>
-      </c>
-      <c r="AG221" t="inlineStr">
-        <is>
-          <t>Holster Dual Leather Ettore</t>
-        </is>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>2046</t>
-        </is>
-      </c>
-      <c r="AI221" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ221" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr"/>
+      <c r="W221" t="inlineStr"/>
+      <c r="X221" t="inlineStr"/>
+      <c r="Y221" t="inlineStr"/>
+      <c r="Z221" t="inlineStr"/>
+      <c r="AA221" t="inlineStr"/>
+      <c r="AB221" t="inlineStr"/>
+      <c r="AC221" t="inlineStr"/>
+      <c r="AD221" t="inlineStr"/>
+      <c r="AE221" t="inlineStr"/>
+      <c r="AF221" t="inlineStr"/>
+      <c r="AG221" t="inlineStr"/>
+      <c r="AH221" t="inlineStr"/>
+      <c r="AI221" t="inlineStr"/>
+      <c r="AJ221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -30152,12 +29796,12 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>0.554</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.480</t>
         </is>
       </c>
       <c r="P223" t="inlineStr"/>
@@ -30167,82 +29811,82 @@
       <c r="T223" t="inlineStr"/>
       <c r="U223" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>0.554</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>Bucket Super Lid Ettore</t>
+          <t>Handheld TDS Meter</t>
         </is>
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>85100</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.480</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>Bucket Super Sieve Ettore</t>
+          <t>Tucker® ACME Tip</t>
         </is>
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>85301</t>
+          <t>T-ACME-TIP-ALUMINUM</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>1 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AG223" t="inlineStr">
         <is>
-          <t>Super Brush Ettore</t>
+          <t>Tucker® Delivery Pump</t>
         </is>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>JRACEN-SUPER-BRUSH</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>1 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -31372,12 +31016,12 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P231" t="inlineStr"/>
@@ -31387,84 +31031,44 @@
       <c r="T231" t="inlineStr"/>
       <c r="U231" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>Large Flo Brush</t>
+          <t>GLIDE Bristle Upgrade For Tucker® Alpha Solar 20" Brush</t>
         </is>
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>59080</t>
+          <t>UGK-20ALPHA-SOLAR-GL</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>0.358</t>
-        </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>Super Brush Ettore</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>JRACEN-SUPER-BRUSH</t>
-        </is>
-      </c>
-      <c r="AD231" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE231" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF231" t="inlineStr">
-        <is>
-          <t>0.354</t>
-        </is>
-      </c>
-      <c r="AG231" t="inlineStr">
-        <is>
-          <t>Flo Brush</t>
-        </is>
-      </c>
-      <c r="AH231" t="inlineStr">
-        <is>
-          <t>59070</t>
-        </is>
-      </c>
-      <c r="AI231" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ231" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>3 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr"/>
+      <c r="AB231" t="inlineStr"/>
+      <c r="AC231" t="inlineStr"/>
+      <c r="AD231" t="inlineStr"/>
+      <c r="AE231" t="inlineStr"/>
+      <c r="AF231" t="inlineStr"/>
+      <c r="AG231" t="inlineStr"/>
+      <c r="AH231" t="inlineStr"/>
+      <c r="AI231" t="inlineStr"/>
+      <c r="AJ231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -32666,12 +32270,12 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>0.646</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>0.380</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="P240" t="inlineStr"/>
@@ -32681,82 +32285,82 @@
       <c r="T240" t="inlineStr"/>
       <c r="U240" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>0.646</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>Auto Squeegee, Repl. Head, 10" Red Sponge</t>
+          <t>2.5 x 10" Sediment Filter</t>
         </is>
       </c>
       <c r="X240" t="inlineStr">
         <is>
-          <t>59010</t>
+          <t>TUCKER-2-5IN-X-10IN-SEDIMENT-FILTER</t>
         </is>
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>0.380</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>Ettore T-Bar ProGrip 10 inch</t>
+          <t>4.5" x 10" Filter Housing</t>
         </is>
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>20040</t>
         </is>
       </c>
       <c r="AD240" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
         <is>
-          <t>0.380</t>
+          <t>0.597</t>
         </is>
       </c>
       <c r="AG240" t="inlineStr">
         <is>
-          <t>Ettore Sleeve Mighty 10 inch</t>
+          <t>Empty 4.5 x 10" Refillable Filter</t>
         </is>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="AI240" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -33536,65 +33140,109 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>exact_base_name</t>
+          <t>unmatched</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.631</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P246" t="inlineStr">
-        <is>
-          <t>3453</t>
-        </is>
-      </c>
-      <c r="Q246" t="inlineStr">
-        <is>
-          <t>76146 KIT CHECK VALVE</t>
-        </is>
-      </c>
-      <c r="R246" t="inlineStr">
+          <t>0.548</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
+      <c r="S246" t="inlineStr"/>
+      <c r="T246" t="inlineStr"/>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>2 shared tokens, name contains match</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>0.631</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>Check Valve 1/2"</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>63042</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>2 shared tokens, name contains match</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>0.548</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>3/4in check valve</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>22211</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>MPWSR</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>2 shared tokens, name contains match</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>0.527</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>CHECK VALVE,1/2"F-NPT</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>7395</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
         <is>
           <t>Barrens</t>
         </is>
       </c>
-      <c r="S246" t="inlineStr"/>
-      <c r="T246" t="inlineStr">
-        <is>
-          <t>14.61</t>
-        </is>
-      </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t>Base product name matches a single catalog item after stripping pack descriptors.</t>
-        </is>
-      </c>
-      <c r="V246" t="inlineStr"/>
-      <c r="W246" t="inlineStr"/>
-      <c r="X246" t="inlineStr"/>
-      <c r="Y246" t="inlineStr"/>
-      <c r="Z246" t="inlineStr"/>
-      <c r="AA246" t="inlineStr"/>
-      <c r="AB246" t="inlineStr"/>
-      <c r="AC246" t="inlineStr"/>
-      <c r="AD246" t="inlineStr"/>
-      <c r="AE246" t="inlineStr"/>
-      <c r="AF246" t="inlineStr"/>
-      <c r="AG246" t="inlineStr"/>
-      <c r="AH246" t="inlineStr"/>
-      <c r="AI246" t="inlineStr"/>
-      <c r="AJ246" t="inlineStr"/>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>2 shared tokens, name contains match</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -34108,22 +33756,22 @@
       <c r="AE250" t="inlineStr"/>
       <c r="AF250" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>0.280</t>
         </is>
       </c>
       <c r="AG250" t="inlineStr">
         <is>
-          <t>VALVE FLOW BALANCE AXD</t>
+          <t>Pigtail Inlet</t>
         </is>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
-          <t>2409009100</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="AI250" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ250" t="inlineStr"/>
@@ -35782,12 +35430,12 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.491</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.480</t>
         </is>
       </c>
       <c r="P262" t="inlineStr"/>
@@ -35797,64 +35445,84 @@
       <c r="T262" t="inlineStr"/>
       <c r="U262" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>4 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V262" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.491</t>
         </is>
       </c>
       <c r="W262" t="inlineStr">
         <is>
-          <t>Holster Dual Nylon Ettore</t>
+          <t>Water Fed Brush │ Dual Trim - Boar &amp; Nylon Bristle Hybrid - 2 Pencil Jets</t>
         </is>
       </c>
       <c r="X262" t="inlineStr">
         <is>
-          <t>50130</t>
+          <t>T-12HY-LT</t>
         </is>
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>4 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.480</t>
         </is>
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>Pole Pro+ Snap-In Tip Nylon Ettore</t>
+          <t>Water Fed Brush│Boar Bristle - 4 Pencil Jets</t>
         </is>
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>JRACEN-PRO-POLE-TIP</t>
+          <t>WATER-FED-BRUSH│BOAR-BRISTLE---4-PENCIL-JETS</t>
         </is>
       </c>
       <c r="AD262" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF262" t="inlineStr"/>
-      <c r="AG262" t="inlineStr"/>
-      <c r="AH262" t="inlineStr"/>
-      <c r="AI262" t="inlineStr"/>
-      <c r="AJ262" t="inlineStr"/>
+          <t>3 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>0.416</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>Pair Of Tucker® Euro Brush Pencil Jets</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>50006-PS</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>2 shared tokens, category fit</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -37676,109 +37344,69 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>0.230</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>0.229</t>
-        </is>
-      </c>
-      <c r="P276" t="inlineStr"/>
-      <c r="Q276" t="inlineStr"/>
-      <c r="R276" t="inlineStr"/>
-      <c r="S276" t="inlineStr"/>
-      <c r="T276" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>60005-V2</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>Tucker® MQC - V2</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>17.68</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>12.38</t>
+        </is>
+      </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>0.230</t>
-        </is>
-      </c>
-      <c r="W276" t="inlineStr">
-        <is>
-          <t>Super Channel 14"</t>
-        </is>
-      </c>
-      <c r="X276" t="inlineStr">
-        <is>
-          <t>JRACEN-SUPER-CHANNEL-14</t>
-        </is>
-      </c>
-      <c r="Y276" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="AA276" t="inlineStr">
-        <is>
-          <t>0.229</t>
-        </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>Bucket Super Caster Ettore</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>85200</t>
-        </is>
-      </c>
-      <c r="AD276" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE276" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="AF276" t="inlineStr">
-        <is>
-          <t>0.228</t>
-        </is>
-      </c>
-      <c r="AG276" t="inlineStr">
-        <is>
-          <t>Bucket Super Compact Lid Ettore</t>
-        </is>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>86100</t>
-        </is>
-      </c>
-      <c r="AI276" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ276" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr"/>
+      <c r="W276" t="inlineStr"/>
+      <c r="X276" t="inlineStr"/>
+      <c r="Y276" t="inlineStr"/>
+      <c r="Z276" t="inlineStr"/>
+      <c r="AA276" t="inlineStr"/>
+      <c r="AB276" t="inlineStr"/>
+      <c r="AC276" t="inlineStr"/>
+      <c r="AD276" t="inlineStr"/>
+      <c r="AE276" t="inlineStr"/>
+      <c r="AF276" t="inlineStr"/>
+      <c r="AG276" t="inlineStr"/>
+      <c r="AH276" t="inlineStr"/>
+      <c r="AI276" t="inlineStr"/>
+      <c r="AJ276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -37844,12 +37472,12 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.664</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.512</t>
         </is>
       </c>
       <c r="P277" t="inlineStr"/>
@@ -37859,82 +37487,82 @@
       <c r="T277" t="inlineStr"/>
       <c r="U277" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.664</t>
         </is>
       </c>
       <c r="W277" t="inlineStr">
         <is>
-          <t>Cleaning Clamp Brush</t>
+          <t>Tucker® MQC - V2</t>
         </is>
       </c>
       <c r="X277" t="inlineStr">
         <is>
-          <t>55170</t>
+          <t>60005-V2</t>
         </is>
       </c>
       <c r="Y277" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.512</t>
         </is>
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>Cleaning Clamp Sponge</t>
+          <t>Tucker® Reach Around Gooseneck V2</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
         <is>
-          <t>55180</t>
+          <t>40001-V2</t>
         </is>
       </c>
       <c r="AD277" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.510</t>
         </is>
       </c>
       <c r="AG277" t="inlineStr">
         <is>
-          <t>Cleaning Clamp Ettore</t>
+          <t>Tucker® Swiveling Gooseneck V2</t>
         </is>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
-          <t>55160</t>
+          <t>T-SWIVEL-V2</t>
         </is>
       </c>
       <c r="AI277" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -38318,12 +37946,12 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>0.616</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.563</t>
         </is>
       </c>
       <c r="P280" t="inlineStr"/>
@@ -38333,82 +37961,82 @@
       <c r="T280" t="inlineStr"/>
       <c r="U280" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>0.616</t>
         </is>
       </c>
       <c r="W280" t="inlineStr">
         <is>
-          <t>Auto Squeegee Scrubber Ettore</t>
+          <t>Tucker® Mini Scrubber</t>
         </is>
       </c>
       <c r="X280" t="inlineStr">
         <is>
-          <t>59016</t>
+          <t>40019</t>
         </is>
       </c>
       <c r="Y280" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.563</t>
         </is>
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>Auto Squeegee Scrubber Wood 8" Head, 25" overall</t>
+          <t>Tucker® Alpha Glide - XL</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
         <is>
-          <t>59020</t>
+          <t>T-18ALPHA-GL</t>
         </is>
       </c>
       <c r="AD280" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.540</t>
         </is>
       </c>
       <c r="AG280" t="inlineStr">
         <is>
-          <t>Auto Squeegee Scrubber Wood 8" Head, 17" overall</t>
+          <t>Tucker® Alpha Honey Badger</t>
         </is>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
-          <t>59816</t>
+          <t>T-12ALPHA-HB-STD</t>
         </is>
       </c>
       <c r="AI280" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -38476,12 +38104,12 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>0.542</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.522</t>
         </is>
       </c>
       <c r="P281" t="inlineStr"/>
@@ -38491,82 +38119,82 @@
       <c r="T281" t="inlineStr"/>
       <c r="U281" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>0.542</t>
         </is>
       </c>
       <c r="W281" t="inlineStr">
         <is>
-          <t>30" Curved Aluminum Floor Squeegee</t>
+          <t>4 x 30" Filter Cartridge - Carbon</t>
         </is>
       </c>
       <c r="X281" t="inlineStr">
         <is>
-          <t>55040</t>
+          <t>20066-C</t>
         </is>
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.522</t>
         </is>
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>Ettore Super Channel Aluminum 30 inch</t>
+          <t>Tucker® - 30 Water Fed Pole</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>TUCKER-30</t>
         </is>
       </c>
       <c r="AD281" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.502</t>
         </is>
       </c>
       <c r="AG281" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 30 inch</t>
+          <t>Tucker® - 30 Water Fed Pole - Bare</t>
         </is>
       </c>
       <c r="AH281" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>ECO-30-BARE</t>
         </is>
       </c>
       <c r="AI281" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -39751,7 +39379,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.452</t>
         </is>
       </c>
       <c r="P290" t="inlineStr"/>
@@ -39791,22 +39419,22 @@
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.452</t>
         </is>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>CABLE, BATTERY RED 6 GAUGE RED</t>
+          <t>Large Battery Box</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
         <is>
-          <t>85.603.040</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="AD290" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE290" t="inlineStr">
@@ -39816,22 +39444,22 @@
       </c>
       <c r="AF290" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>0.452</t>
         </is>
       </c>
       <c r="AG290" t="inlineStr">
         <is>
-          <t>CABLE, BATTERY BLK 6 GAUGE BLACK</t>
+          <t>Battery Hold-Down</t>
         </is>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
-          <t>85.603.041</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="AI290" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ290" t="inlineStr">
@@ -41028,12 +40656,12 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.609</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.591</t>
         </is>
       </c>
       <c r="P299" t="inlineStr"/>
@@ -41043,82 +40671,82 @@
       <c r="T299" t="inlineStr"/>
       <c r="U299" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.609</t>
         </is>
       </c>
       <c r="W299" t="inlineStr">
         <is>
-          <t>Ettore MicroSwipe Microfiber Towel 10 Pack Blue</t>
+          <t>2.5 x 10" Sediment / Carbon Combo Filter</t>
         </is>
       </c>
       <c r="X299" t="inlineStr">
         <is>
-          <t>84410</t>
+          <t>20025/26</t>
         </is>
       </c>
       <c r="Y299" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.591</t>
         </is>
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>Auto Squeegee, Repl. Head, 10" Red Sponge</t>
+          <t>2.5 x 10" Sediment Filter</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>59010</t>
+          <t>TUCKER-2-5IN-X-10IN-SEDIMENT-FILTER</t>
         </is>
       </c>
       <c r="AD299" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.566</t>
         </is>
       </c>
       <c r="AG299" t="inlineStr">
         <is>
-          <t>Ettore T-Bar ProGrip 10 inch</t>
+          <t>Empty 4.5 x 10" Refillable Filter</t>
         </is>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="AI299" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -42234,17 +41862,17 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
@@ -42252,41 +41880,41 @@
           <t>0.000</t>
         </is>
       </c>
-      <c r="P307" t="inlineStr"/>
-      <c r="Q307" t="inlineStr"/>
-      <c r="R307" t="inlineStr"/>
-      <c r="S307" t="inlineStr"/>
-      <c r="T307" t="inlineStr"/>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>20029</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>Empty 4.5 x 10" Refillable Filter</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>30.06</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>21.05</t>
+        </is>
+      </c>
       <c r="U307" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V307" t="inlineStr">
-        <is>
-          <t>0.267</t>
-        </is>
-      </c>
-      <c r="W307" t="inlineStr">
-        <is>
-          <t>Blades 4in for HD Scraper (10) Ettore</t>
-        </is>
-      </c>
-      <c r="X307" t="inlineStr">
-        <is>
-          <t>20291</t>
-        </is>
-      </c>
-      <c r="Y307" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z307" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr"/>
+      <c r="W307" t="inlineStr"/>
+      <c r="X307" t="inlineStr"/>
+      <c r="Y307" t="inlineStr"/>
+      <c r="Z307" t="inlineStr"/>
       <c r="AA307" t="inlineStr"/>
       <c r="AB307" t="inlineStr"/>
       <c r="AC307" t="inlineStr"/>
@@ -42510,17 +42138,17 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>0.330</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
@@ -42528,41 +42156,41 @@
           <t>0.000</t>
         </is>
       </c>
-      <c r="P309" t="inlineStr"/>
-      <c r="Q309" t="inlineStr"/>
-      <c r="R309" t="inlineStr"/>
-      <c r="S309" t="inlineStr"/>
-      <c r="T309" t="inlineStr"/>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>20027</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>4 x 10in DI Cartridge Blue/White</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>103.72</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>72.60</t>
+        </is>
+      </c>
       <c r="U309" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V309" t="inlineStr">
-        <is>
-          <t>0.330</t>
-        </is>
-      </c>
-      <c r="W309" t="inlineStr">
-        <is>
-          <t>T-bar and Golden Glove Sleeve 10in Ettore</t>
-        </is>
-      </c>
-      <c r="X309" t="inlineStr">
-        <is>
-          <t>JRACEN-GOLDEN-GLOVE-WASHER-COMPLETE-SLE</t>
-        </is>
-      </c>
-      <c r="Y309" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z309" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr"/>
+      <c r="W309" t="inlineStr"/>
+      <c r="X309" t="inlineStr"/>
+      <c r="Y309" t="inlineStr"/>
+      <c r="Z309" t="inlineStr"/>
       <c r="AA309" t="inlineStr"/>
       <c r="AB309" t="inlineStr"/>
       <c r="AC309" t="inlineStr"/>
@@ -45720,12 +45348,12 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="P333" t="inlineStr"/>
@@ -45735,82 +45363,82 @@
       <c r="T333" t="inlineStr"/>
       <c r="U333" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V333" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="W333" t="inlineStr">
         <is>
-          <t>Cleaning Clamp Brush</t>
+          <t>LOCT Adjustable Tucker Gooseneck w/ Quick Release for #1 Clamp</t>
         </is>
       </c>
       <c r="X333" t="inlineStr">
         <is>
-          <t>55170</t>
+          <t>T-GN-V2-LT</t>
         </is>
       </c>
       <c r="Y333" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>Cleaning Clamp Sponge</t>
+          <t>Number 1 Clamp w/ all hardware Tucker® V2</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
         <is>
-          <t>55180</t>
+          <t>T-T1-V2-COMPLETE</t>
         </is>
       </c>
       <c r="AD333" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>0.235</t>
         </is>
       </c>
       <c r="AG333" t="inlineStr">
         <is>
-          <t>Cleaning Clamp Ettore</t>
+          <t>Number 9 Clamp w/all hardware Tucker® V2</t>
         </is>
       </c>
       <c r="AH333" t="inlineStr">
         <is>
-          <t>55160</t>
+          <t>T-T9-V2-COMPLETE</t>
         </is>
       </c>
       <c r="AI333" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -48614,109 +48242,69 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>0.274</t>
-        </is>
-      </c>
-      <c r="P353" t="inlineStr"/>
-      <c r="Q353" t="inlineStr"/>
-      <c r="R353" t="inlineStr"/>
-      <c r="S353" t="inlineStr"/>
-      <c r="T353" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>T-OTT-XL-V2-P</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>Tucker® Over the Top Rinse Bar Large PLASTIC</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>63.12</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>44.19</t>
+        </is>
+      </c>
       <c r="U353" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V353" t="inlineStr">
-        <is>
-          <t>0.274</t>
-        </is>
-      </c>
-      <c r="W353" t="inlineStr">
-        <is>
-          <t>Ettore T-Bar Taper Plastic 18 inch</t>
-        </is>
-      </c>
-      <c r="X353" t="inlineStr">
-        <is>
-          <t>JRACEN-TAPER-T-BAR-T-BAR-18</t>
-        </is>
-      </c>
-      <c r="Y353" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z353" t="inlineStr">
-        <is>
-          <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA353" t="inlineStr">
-        <is>
-          <t>0.274</t>
-        </is>
-      </c>
-      <c r="AB353" t="inlineStr">
-        <is>
-          <t>Ettore T-Bar Taper Plastic 14 inch</t>
-        </is>
-      </c>
-      <c r="AC353" t="inlineStr">
-        <is>
-          <t>JRACEN-TAPER-T-BAR-T-BAR-14</t>
-        </is>
-      </c>
-      <c r="AD353" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE353" t="inlineStr">
-        <is>
-          <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF353" t="inlineStr">
-        <is>
-          <t>0.274</t>
-        </is>
-      </c>
-      <c r="AG353" t="inlineStr">
-        <is>
-          <t>Ettore T-Bar Taper Plastic 10 inch</t>
-        </is>
-      </c>
-      <c r="AH353" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="AI353" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ353" t="inlineStr">
-        <is>
-          <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr"/>
+      <c r="W353" t="inlineStr"/>
+      <c r="X353" t="inlineStr"/>
+      <c r="Y353" t="inlineStr"/>
+      <c r="Z353" t="inlineStr"/>
+      <c r="AA353" t="inlineStr"/>
+      <c r="AB353" t="inlineStr"/>
+      <c r="AC353" t="inlineStr"/>
+      <c r="AD353" t="inlineStr"/>
+      <c r="AE353" t="inlineStr"/>
+      <c r="AF353" t="inlineStr"/>
+      <c r="AG353" t="inlineStr"/>
+      <c r="AH353" t="inlineStr"/>
+      <c r="AI353" t="inlineStr"/>
+      <c r="AJ353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -48772,109 +48360,69 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>0.368</t>
-        </is>
-      </c>
-      <c r="P354" t="inlineStr"/>
-      <c r="Q354" t="inlineStr"/>
-      <c r="R354" t="inlineStr"/>
-      <c r="S354" t="inlineStr"/>
-      <c r="T354" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>60040</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>Female Quick Connect for Pole Hose</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>13.67</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
       <c r="U354" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V354" t="inlineStr">
-        <is>
-          <t>0.368</t>
-        </is>
-      </c>
-      <c r="W354" t="inlineStr">
-        <is>
-          <t>Ettore Interlock Telescopic Pole 4 foot</t>
-        </is>
-      </c>
-      <c r="X354" t="inlineStr">
-        <is>
-          <t>42005</t>
-        </is>
-      </c>
-      <c r="Y354" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z354" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA354" t="inlineStr">
-        <is>
-          <t>0.368</t>
-        </is>
-      </c>
-      <c r="AB354" t="inlineStr">
-        <is>
-          <t>Ettore Interlock Telescopic Pole 2 foot</t>
-        </is>
-      </c>
-      <c r="AC354" t="inlineStr">
-        <is>
-          <t>42003</t>
-        </is>
-      </c>
-      <c r="AD354" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE354" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF354" t="inlineStr">
-        <is>
-          <t>0.366</t>
-        </is>
-      </c>
-      <c r="AG354" t="inlineStr">
-        <is>
-          <t>Handle Kit Quick Release Ettore</t>
-        </is>
-      </c>
-      <c r="AH354" t="inlineStr">
-        <is>
-          <t>JRACEN-QUICK-RELEASE-KIT</t>
-        </is>
-      </c>
-      <c r="AI354" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ354" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr"/>
+      <c r="W354" t="inlineStr"/>
+      <c r="X354" t="inlineStr"/>
+      <c r="Y354" t="inlineStr"/>
+      <c r="Z354" t="inlineStr"/>
+      <c r="AA354" t="inlineStr"/>
+      <c r="AB354" t="inlineStr"/>
+      <c r="AC354" t="inlineStr"/>
+      <c r="AD354" t="inlineStr"/>
+      <c r="AE354" t="inlineStr"/>
+      <c r="AF354" t="inlineStr"/>
+      <c r="AG354" t="inlineStr"/>
+      <c r="AH354" t="inlineStr"/>
+      <c r="AI354" t="inlineStr"/>
+      <c r="AJ354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -51702,109 +51250,69 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>0.248</t>
-        </is>
-      </c>
-      <c r="P375" t="inlineStr"/>
-      <c r="Q375" t="inlineStr"/>
-      <c r="R375" t="inlineStr"/>
-      <c r="S375" t="inlineStr"/>
-      <c r="T375" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>20066</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>4 x 30" Filter Cartridge - Refillable</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>57.87</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>40.51</t>
+        </is>
+      </c>
       <c r="U375" t="inlineStr">
         <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="V375" t="inlineStr">
-        <is>
-          <t>0.251</t>
-        </is>
-      </c>
-      <c r="W375" t="inlineStr">
-        <is>
-          <t>Mini Blind Duster Ettore</t>
-        </is>
-      </c>
-      <c r="X375" t="inlineStr">
-        <is>
-          <t>48213</t>
-        </is>
-      </c>
-      <c r="Y375" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z375" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="AA375" t="inlineStr">
-        <is>
-          <t>0.248</t>
-        </is>
-      </c>
-      <c r="AB375" t="inlineStr">
-        <is>
-          <t>Holster Master Leather Ettore</t>
-        </is>
-      </c>
-      <c r="AC375" t="inlineStr">
-        <is>
-          <t>JRACEN-LEATHER-HOLSTER</t>
-        </is>
-      </c>
-      <c r="AD375" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE375" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="AF375" t="inlineStr">
-        <is>
-          <t>0.236</t>
-        </is>
-      </c>
-      <c r="AG375" t="inlineStr">
-        <is>
-          <t>Window Cleaning Display</t>
-        </is>
-      </c>
-      <c r="AH375" t="inlineStr">
-        <is>
-          <t>47002</t>
-        </is>
-      </c>
-      <c r="AI375" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ375" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr"/>
+      <c r="W375" t="inlineStr"/>
+      <c r="X375" t="inlineStr"/>
+      <c r="Y375" t="inlineStr"/>
+      <c r="Z375" t="inlineStr"/>
+      <c r="AA375" t="inlineStr"/>
+      <c r="AB375" t="inlineStr"/>
+      <c r="AC375" t="inlineStr"/>
+      <c r="AD375" t="inlineStr"/>
+      <c r="AE375" t="inlineStr"/>
+      <c r="AF375" t="inlineStr"/>
+      <c r="AG375" t="inlineStr"/>
+      <c r="AH375" t="inlineStr"/>
+      <c r="AI375" t="inlineStr"/>
+      <c r="AJ375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -53074,109 +52582,69 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>0.237</t>
-        </is>
-      </c>
-      <c r="P385" t="inlineStr"/>
-      <c r="Q385" t="inlineStr"/>
-      <c r="R385" t="inlineStr"/>
-      <c r="S385" t="inlineStr"/>
-      <c r="T385" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>T-OTT-STD-V2</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Tucker® Over the Top Rinse Bar Small - Plastic</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>50.49</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>35.34</t>
+        </is>
+      </c>
       <c r="U385" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V385" t="inlineStr">
-        <is>
-          <t>0.237</t>
-        </is>
-      </c>
-      <c r="W385" t="inlineStr">
-        <is>
-          <t>Ettore T-Bar ProGrip 18 inch</t>
-        </is>
-      </c>
-      <c r="X385" t="inlineStr">
-        <is>
-          <t>JRACEN-PRO-GRIP-T-BAR-18</t>
-        </is>
-      </c>
-      <c r="Y385" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z385" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA385" t="inlineStr">
-        <is>
-          <t>0.237</t>
-        </is>
-      </c>
-      <c r="AB385" t="inlineStr">
-        <is>
-          <t>Ettore T-Bar ProGrip 14 inch</t>
-        </is>
-      </c>
-      <c r="AC385" t="inlineStr">
-        <is>
-          <t>JRACEN-PRO-GRIP-T-BAR-14</t>
-        </is>
-      </c>
-      <c r="AD385" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE385" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF385" t="inlineStr">
-        <is>
-          <t>0.237</t>
-        </is>
-      </c>
-      <c r="AG385" t="inlineStr">
-        <is>
-          <t>Ettore T-Bar ProGrip 10 inch</t>
-        </is>
-      </c>
-      <c r="AH385" t="inlineStr">
-        <is>
-          <t>4010</t>
-        </is>
-      </c>
-      <c r="AI385" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ385" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr"/>
+      <c r="W385" t="inlineStr"/>
+      <c r="X385" t="inlineStr"/>
+      <c r="Y385" t="inlineStr"/>
+      <c r="Z385" t="inlineStr"/>
+      <c r="AA385" t="inlineStr"/>
+      <c r="AB385" t="inlineStr"/>
+      <c r="AC385" t="inlineStr"/>
+      <c r="AD385" t="inlineStr"/>
+      <c r="AE385" t="inlineStr"/>
+      <c r="AF385" t="inlineStr"/>
+      <c r="AG385" t="inlineStr"/>
+      <c r="AH385" t="inlineStr"/>
+      <c r="AI385" t="inlineStr"/>
+      <c r="AJ385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -53390,109 +52858,69 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>0.317</t>
-        </is>
-      </c>
-      <c r="P387" t="inlineStr"/>
-      <c r="Q387" t="inlineStr"/>
-      <c r="R387" t="inlineStr"/>
-      <c r="S387" t="inlineStr"/>
-      <c r="T387" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>63014</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>Union for Pole Tubing</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>3.83</t>
+        </is>
+      </c>
       <c r="U387" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V387" t="inlineStr">
-        <is>
-          <t>0.329</t>
-        </is>
-      </c>
-      <c r="W387" t="inlineStr">
-        <is>
-          <t>Ettore Grip-n-Grab Tool 16 inch</t>
-        </is>
-      </c>
-      <c r="X387" t="inlineStr">
-        <is>
-          <t>49016</t>
-        </is>
-      </c>
-      <c r="Y387" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z387" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA387" t="inlineStr">
-        <is>
-          <t>0.317</t>
-        </is>
-      </c>
-      <c r="AB387" t="inlineStr">
-        <is>
-          <t>Ettore All Purpose Squeegees 16 inch</t>
-        </is>
-      </c>
-      <c r="AC387" t="inlineStr">
-        <is>
-          <t>17016</t>
-        </is>
-      </c>
-      <c r="AD387" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE387" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF387" t="inlineStr">
-        <is>
-          <t>0.316</t>
-        </is>
-      </c>
-      <c r="AG387" t="inlineStr">
-        <is>
-          <t>Pro+ Squeegee Complete 16"</t>
-        </is>
-      </c>
-      <c r="AH387" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="AI387" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ387" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr"/>
+      <c r="W387" t="inlineStr"/>
+      <c r="X387" t="inlineStr"/>
+      <c r="Y387" t="inlineStr"/>
+      <c r="Z387" t="inlineStr"/>
+      <c r="AA387" t="inlineStr"/>
+      <c r="AB387" t="inlineStr"/>
+      <c r="AC387" t="inlineStr"/>
+      <c r="AD387" t="inlineStr"/>
+      <c r="AE387" t="inlineStr"/>
+      <c r="AF387" t="inlineStr"/>
+      <c r="AG387" t="inlineStr"/>
+      <c r="AH387" t="inlineStr"/>
+      <c r="AI387" t="inlineStr"/>
+      <c r="AJ387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -56668,109 +56096,69 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>0.331</t>
-        </is>
-      </c>
-      <c r="P410" t="inlineStr"/>
-      <c r="Q410" t="inlineStr"/>
-      <c r="R410" t="inlineStr"/>
-      <c r="S410" t="inlineStr"/>
-      <c r="T410" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>T-ACME-TIP-ALUMINUM</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>Tucker® ACME Tip</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>11.22</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>7.86</t>
+        </is>
+      </c>
       <c r="U410" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V410" t="inlineStr">
-        <is>
-          <t>0.334</t>
-        </is>
-      </c>
-      <c r="W410" t="inlineStr">
-        <is>
-          <t>Cleaning Clamp Brush</t>
-        </is>
-      </c>
-      <c r="X410" t="inlineStr">
-        <is>
-          <t>55170</t>
-        </is>
-      </c>
-      <c r="Y410" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z410" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA410" t="inlineStr">
-        <is>
-          <t>0.331</t>
-        </is>
-      </c>
-      <c r="AB410" t="inlineStr">
-        <is>
-          <t>Ettore REA-C-H Aluminum Extension Poles 9 foot</t>
-        </is>
-      </c>
-      <c r="AC410" t="inlineStr">
-        <is>
-          <t>1680</t>
-        </is>
-      </c>
-      <c r="AD410" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE410" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF410" t="inlineStr">
-        <is>
-          <t>0.331</t>
-        </is>
-      </c>
-      <c r="AG410" t="inlineStr">
-        <is>
-          <t>Ettore REA-C-H Aluminum Extension Poles 8 foot</t>
-        </is>
-      </c>
-      <c r="AH410" t="inlineStr">
-        <is>
-          <t>42108</t>
-        </is>
-      </c>
-      <c r="AI410" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ410" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr"/>
+      <c r="W410" t="inlineStr"/>
+      <c r="X410" t="inlineStr"/>
+      <c r="Y410" t="inlineStr"/>
+      <c r="Z410" t="inlineStr"/>
+      <c r="AA410" t="inlineStr"/>
+      <c r="AB410" t="inlineStr"/>
+      <c r="AC410" t="inlineStr"/>
+      <c r="AD410" t="inlineStr"/>
+      <c r="AE410" t="inlineStr"/>
+      <c r="AF410" t="inlineStr"/>
+      <c r="AG410" t="inlineStr"/>
+      <c r="AH410" t="inlineStr"/>
+      <c r="AI410" t="inlineStr"/>
+      <c r="AJ410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -57666,84 +57054,64 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_name</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t>0.300</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>0.257</t>
-        </is>
-      </c>
-      <c r="P417" t="inlineStr"/>
-      <c r="Q417" t="inlineStr"/>
-      <c r="R417" t="inlineStr"/>
-      <c r="S417" t="inlineStr"/>
-      <c r="T417" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>T-ACME-TIP-ALUMINUM</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>Tucker® ACME Tip</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>11.22</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>7.86</t>
+        </is>
+      </c>
       <c r="U417" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V417" t="inlineStr">
-        <is>
-          <t>0.300</t>
-        </is>
-      </c>
-      <c r="W417" t="inlineStr">
-        <is>
-          <t>Pole Pro+ Snap-In Tip Nylon Ettore</t>
-        </is>
-      </c>
-      <c r="X417" t="inlineStr">
-        <is>
-          <t>JRACEN-PRO-POLE-TIP</t>
-        </is>
-      </c>
-      <c r="Y417" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z417" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA417" t="inlineStr">
-        <is>
-          <t>0.257</t>
-        </is>
-      </c>
-      <c r="AB417" t="inlineStr">
-        <is>
-          <t>Ettore Utility Pole 60in ACME Thread</t>
-        </is>
-      </c>
-      <c r="AC417" t="inlineStr">
-        <is>
-          <t>42100</t>
-        </is>
-      </c>
-      <c r="AD417" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE417" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Normalized sales item name exactly matches the catalog name.</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr"/>
+      <c r="W417" t="inlineStr"/>
+      <c r="X417" t="inlineStr"/>
+      <c r="Y417" t="inlineStr"/>
+      <c r="Z417" t="inlineStr"/>
+      <c r="AA417" t="inlineStr"/>
+      <c r="AB417" t="inlineStr"/>
+      <c r="AC417" t="inlineStr"/>
+      <c r="AD417" t="inlineStr"/>
+      <c r="AE417" t="inlineStr"/>
       <c r="AF417" t="inlineStr"/>
       <c r="AG417" t="inlineStr"/>
       <c r="AH417" t="inlineStr"/>
@@ -59370,109 +58738,69 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>0.281</t>
-        </is>
-      </c>
-      <c r="P429" t="inlineStr"/>
-      <c r="Q429" t="inlineStr"/>
-      <c r="R429" t="inlineStr"/>
-      <c r="S429" t="inlineStr"/>
-      <c r="T429" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>T-WCT</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>Wood Cone Tip</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>4.31</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
       <c r="U429" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V429" t="inlineStr">
-        <is>
-          <t>0.331</t>
-        </is>
-      </c>
-      <c r="W429" t="inlineStr">
-        <is>
-          <t>Pole Pro+ Snap-In Tip Nylon Ettore</t>
-        </is>
-      </c>
-      <c r="X429" t="inlineStr">
-        <is>
-          <t>JRACEN-PRO-POLE-TIP</t>
-        </is>
-      </c>
-      <c r="Y429" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z429" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA429" t="inlineStr">
-        <is>
-          <t>0.281</t>
-        </is>
-      </c>
-      <c r="AB429" t="inlineStr">
-        <is>
-          <t>Ettore Utility Pole 60in ACME Thread</t>
-        </is>
-      </c>
-      <c r="AC429" t="inlineStr">
-        <is>
-          <t>42100</t>
-        </is>
-      </c>
-      <c r="AD429" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE429" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF429" t="inlineStr">
-        <is>
-          <t>0.218</t>
-        </is>
-      </c>
-      <c r="AG429" t="inlineStr">
-        <is>
-          <t>Floor Squeegee Handle 54in Wood Ettore</t>
-        </is>
-      </c>
-      <c r="AH429" t="inlineStr">
-        <is>
-          <t>JRACEN-WOODEN-FLOOR-SQUEEGEE-HANDLES-54</t>
-        </is>
-      </c>
-      <c r="AI429" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ429" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V429" t="inlineStr"/>
+      <c r="W429" t="inlineStr"/>
+      <c r="X429" t="inlineStr"/>
+      <c r="Y429" t="inlineStr"/>
+      <c r="Z429" t="inlineStr"/>
+      <c r="AA429" t="inlineStr"/>
+      <c r="AB429" t="inlineStr"/>
+      <c r="AC429" t="inlineStr"/>
+      <c r="AD429" t="inlineStr"/>
+      <c r="AE429" t="inlineStr"/>
+      <c r="AF429" t="inlineStr"/>
+      <c r="AG429" t="inlineStr"/>
+      <c r="AH429" t="inlineStr"/>
+      <c r="AI429" t="inlineStr"/>
+      <c r="AJ429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -60900,109 +60228,69 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>0.334</t>
-        </is>
-      </c>
-      <c r="P440" t="inlineStr"/>
-      <c r="Q440" t="inlineStr"/>
-      <c r="R440" t="inlineStr"/>
-      <c r="S440" t="inlineStr"/>
-      <c r="T440" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>T-EURO-TIP-PLASTIC</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>Tucker® Euro Tip</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
       <c r="U440" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V440" t="inlineStr">
-        <is>
-          <t>0.338</t>
-        </is>
-      </c>
-      <c r="W440" t="inlineStr">
-        <is>
-          <t>Cleaning Clamp Brush</t>
-        </is>
-      </c>
-      <c r="X440" t="inlineStr">
-        <is>
-          <t>55170</t>
-        </is>
-      </c>
-      <c r="Y440" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z440" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA440" t="inlineStr">
-        <is>
-          <t>0.334</t>
-        </is>
-      </c>
-      <c r="AB440" t="inlineStr">
-        <is>
-          <t>Cleaning Clamp Sponge</t>
-        </is>
-      </c>
-      <c r="AC440" t="inlineStr">
-        <is>
-          <t>55180</t>
-        </is>
-      </c>
-      <c r="AD440" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE440" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF440" t="inlineStr">
-        <is>
-          <t>0.334</t>
-        </is>
-      </c>
-      <c r="AG440" t="inlineStr">
-        <is>
-          <t>Cleaning Clamp Ettore</t>
-        </is>
-      </c>
-      <c r="AH440" t="inlineStr">
-        <is>
-          <t>55160</t>
-        </is>
-      </c>
-      <c r="AI440" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ440" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr"/>
+      <c r="W440" t="inlineStr"/>
+      <c r="X440" t="inlineStr"/>
+      <c r="Y440" t="inlineStr"/>
+      <c r="Z440" t="inlineStr"/>
+      <c r="AA440" t="inlineStr"/>
+      <c r="AB440" t="inlineStr"/>
+      <c r="AC440" t="inlineStr"/>
+      <c r="AD440" t="inlineStr"/>
+      <c r="AE440" t="inlineStr"/>
+      <c r="AF440" t="inlineStr"/>
+      <c r="AG440" t="inlineStr"/>
+      <c r="AH440" t="inlineStr"/>
+      <c r="AI440" t="inlineStr"/>
+      <c r="AJ440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -61864,12 +61152,12 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>0.340</t>
         </is>
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.328</t>
         </is>
       </c>
       <c r="P447" t="inlineStr"/>
@@ -61879,84 +61167,64 @@
       <c r="T447" t="inlineStr"/>
       <c r="U447" t="inlineStr">
         <is>
-          <t>1 shared tokens</t>
+          <t>2 shared tokens</t>
         </is>
       </c>
       <c r="V447" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>0.340</t>
         </is>
       </c>
       <c r="W447" t="inlineStr">
         <is>
-          <t>OPTIONAL 5" QC EXTENSION KIT</t>
+          <t>CF Pole Extension</t>
         </is>
       </c>
       <c r="X447" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>90100-CF-EXT</t>
         </is>
       </c>
       <c r="Y447" t="inlineStr">
         <is>
-          <t>Barrens</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z447" t="inlineStr">
         <is>
-          <t>1 shared tokens</t>
+          <t>2 shared tokens</t>
         </is>
       </c>
       <c r="AA447" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.328</t>
         </is>
       </c>
       <c r="AB447" t="inlineStr">
         <is>
-          <t>REA-C-H Extension Poles 3- Sec, 27'</t>
+          <t>FG Pole Extension #10 Section</t>
         </is>
       </c>
       <c r="AC447" t="inlineStr">
         <is>
-          <t>JRACEN-REA-C-H-EXTENSION-POLES-3-SEC-27</t>
+          <t>T-FG-EXT-WC</t>
         </is>
       </c>
       <c r="AD447" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>1 shared tokens</t>
-        </is>
-      </c>
-      <c r="AF447" t="inlineStr">
-        <is>
-          <t>0.304</t>
-        </is>
-      </c>
-      <c r="AG447" t="inlineStr">
-        <is>
-          <t>OPTIONAL 12" QC EXTENSION KIT</t>
-        </is>
-      </c>
-      <c r="AH447" t="inlineStr">
-        <is>
-          <t>4576</t>
-        </is>
-      </c>
-      <c r="AI447" t="inlineStr">
-        <is>
-          <t>Barrens</t>
-        </is>
-      </c>
-      <c r="AJ447" t="inlineStr">
-        <is>
-          <t>1 shared tokens</t>
-        </is>
-      </c>
+          <t>2 shared tokens</t>
+        </is>
+      </c>
+      <c r="AF447" t="inlineStr"/>
+      <c r="AG447" t="inlineStr"/>
+      <c r="AH447" t="inlineStr"/>
+      <c r="AI447" t="inlineStr"/>
+      <c r="AJ447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -62802,84 +62070,64 @@
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t>0.280</t>
-        </is>
-      </c>
-      <c r="P453" t="inlineStr"/>
-      <c r="Q453" t="inlineStr"/>
-      <c r="R453" t="inlineStr"/>
-      <c r="S453" t="inlineStr"/>
-      <c r="T453" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>63009</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>1/2" FNPT x FGH Swivel Inlet</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>13.67</t>
+        </is>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
       <c r="U453" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V453" t="inlineStr">
-        <is>
-          <t>0.298</t>
-        </is>
-      </c>
-      <c r="W453" t="inlineStr">
-        <is>
-          <t>Bucket 3 1/2 Gal Ettore Round - each</t>
-        </is>
-      </c>
-      <c r="X453" t="inlineStr">
-        <is>
-          <t>82222</t>
-        </is>
-      </c>
-      <c r="Y453" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z453" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA453" t="inlineStr">
-        <is>
-          <t>0.280</t>
-        </is>
-      </c>
-      <c r="AB453" t="inlineStr">
-        <is>
-          <t>Floor Squeegee Handle Metal 60in Ettore</t>
-        </is>
-      </c>
-      <c r="AC453" t="inlineStr">
-        <is>
-          <t>61060</t>
-        </is>
-      </c>
-      <c r="AD453" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE453" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V453" t="inlineStr"/>
+      <c r="W453" t="inlineStr"/>
+      <c r="X453" t="inlineStr"/>
+      <c r="Y453" t="inlineStr"/>
+      <c r="Z453" t="inlineStr"/>
+      <c r="AA453" t="inlineStr"/>
+      <c r="AB453" t="inlineStr"/>
+      <c r="AC453" t="inlineStr"/>
+      <c r="AD453" t="inlineStr"/>
+      <c r="AE453" t="inlineStr"/>
       <c r="AF453" t="inlineStr"/>
       <c r="AG453" t="inlineStr"/>
       <c r="AH453" t="inlineStr"/>
@@ -63380,12 +62628,12 @@
       </c>
       <c r="N457" t="inlineStr">
         <is>
+          <t>0.396</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
           <t>0.373</t>
-        </is>
-      </c>
-      <c r="O457" t="inlineStr">
-        <is>
-          <t>0.372</t>
         </is>
       </c>
       <c r="P457" t="inlineStr"/>
@@ -63400,72 +62648,72 @@
       </c>
       <c r="V457" t="inlineStr">
         <is>
+          <t>0.396</t>
+        </is>
+      </c>
+      <c r="W457" t="inlineStr">
+        <is>
+          <t>CARBON Filter Bracket</t>
+        </is>
+      </c>
+      <c r="X457" t="inlineStr">
+        <is>
+          <t>T-1000-003</t>
+        </is>
+      </c>
+      <c r="Y457" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="Z457" t="inlineStr">
+        <is>
+          <t>1 shared tokens</t>
+        </is>
+      </c>
+      <c r="AA457" t="inlineStr">
+        <is>
           <t>0.373</t>
         </is>
       </c>
-      <c r="W457" t="inlineStr">
+      <c r="AB457" t="inlineStr">
         <is>
           <t>Graco Long Filter</t>
         </is>
       </c>
-      <c r="X457" t="inlineStr">
+      <c r="AC457" t="inlineStr">
         <is>
           <t>14-2695</t>
         </is>
       </c>
-      <c r="Y457" t="inlineStr">
+      <c r="AD457" t="inlineStr">
         <is>
           <t>MPWSR</t>
         </is>
       </c>
-      <c r="Z457" t="inlineStr">
+      <c r="AE457" t="inlineStr">
         <is>
           <t>1 shared tokens</t>
         </is>
       </c>
-      <c r="AA457" t="inlineStr">
-        <is>
-          <t>0.372</t>
-        </is>
-      </c>
-      <c r="AB457" t="inlineStr">
-        <is>
-          <t>DURAVIEW INLET FILTER 3/8"MPT, NO PORTS</t>
-        </is>
-      </c>
-      <c r="AC457" t="inlineStr">
-        <is>
-          <t>5181</t>
-        </is>
-      </c>
-      <c r="AD457" t="inlineStr">
-        <is>
-          <t>Barrens</t>
-        </is>
-      </c>
-      <c r="AE457" t="inlineStr">
-        <is>
-          <t>1 shared tokens</t>
-        </is>
-      </c>
       <c r="AF457" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.373</t>
         </is>
       </c>
       <c r="AG457" t="inlineStr">
         <is>
-          <t>SCREEN, FILTER 1" SS</t>
+          <t>DI Filter Bracket</t>
         </is>
       </c>
       <c r="AH457" t="inlineStr">
         <is>
-          <t>85.309.050</t>
+          <t>T-1000-004</t>
         </is>
       </c>
       <c r="AI457" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ457" t="inlineStr">
@@ -66148,12 +65396,12 @@
       </c>
       <c r="N477" t="inlineStr">
         <is>
+          <t>0.426</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
           <t>0.390</t>
-        </is>
-      </c>
-      <c r="O477" t="inlineStr">
-        <is>
-          <t>0.288</t>
         </is>
       </c>
       <c r="P477" t="inlineStr"/>
@@ -66168,59 +65416,79 @@
       </c>
       <c r="V477" t="inlineStr">
         <is>
+          <t>0.426</t>
+        </is>
+      </c>
+      <c r="W477" t="inlineStr">
+        <is>
+          <t>3/8 barb x 1/4 male thread</t>
+        </is>
+      </c>
+      <c r="X477" t="inlineStr">
+        <is>
+          <t>63002</t>
+        </is>
+      </c>
+      <c r="Y477" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="Z477" t="inlineStr">
+        <is>
+          <t>2 shared tokens</t>
+        </is>
+      </c>
+      <c r="AA477" t="inlineStr">
+        <is>
           <t>0.390</t>
         </is>
       </c>
-      <c r="W477" t="inlineStr">
+      <c r="AB477" t="inlineStr">
         <is>
           <t>Banjo Poly 2" Male Thread x 2" Hose Barb</t>
         </is>
       </c>
-      <c r="X477" t="inlineStr">
+      <c r="AC477" t="inlineStr">
         <is>
           <t>BHB200</t>
         </is>
       </c>
-      <c r="Y477" t="inlineStr">
+      <c r="AD477" t="inlineStr">
         <is>
           <t>MPWSR</t>
         </is>
       </c>
-      <c r="Z477" t="inlineStr">
+      <c r="AE477" t="inlineStr">
         <is>
           <t>2 shared tokens</t>
         </is>
       </c>
-      <c r="AA477" t="inlineStr">
-        <is>
-          <t>0.288</t>
-        </is>
-      </c>
-      <c r="AB477" t="inlineStr">
-        <is>
-          <t>PUSH ON HOSE BARB 1/4 HOSE X 1/4 MPT - Thread PushLock</t>
-        </is>
-      </c>
-      <c r="AC477" t="inlineStr">
-        <is>
-          <t>30201</t>
-        </is>
-      </c>
-      <c r="AD477" t="inlineStr">
-        <is>
-          <t>MPWSR</t>
-        </is>
-      </c>
-      <c r="AE477" t="inlineStr">
+      <c r="AF477" t="inlineStr">
+        <is>
+          <t>0.364</t>
+        </is>
+      </c>
+      <c r="AG477" t="inlineStr">
+        <is>
+          <t>3/8 barb x 1/2 male thread</t>
+        </is>
+      </c>
+      <c r="AH477" t="inlineStr">
+        <is>
+          <t>63001</t>
+        </is>
+      </c>
+      <c r="AI477" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="AJ477" t="inlineStr">
         <is>
           <t>2 shared tokens</t>
         </is>
       </c>
-      <c r="AF477" t="inlineStr"/>
-      <c r="AG477" t="inlineStr"/>
-      <c r="AH477" t="inlineStr"/>
-      <c r="AI477" t="inlineStr"/>
-      <c r="AJ477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -66982,109 +66250,69 @@
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t>0.298</t>
-        </is>
-      </c>
-      <c r="P483" t="inlineStr"/>
-      <c r="Q483" t="inlineStr"/>
-      <c r="R483" t="inlineStr"/>
-      <c r="S483" t="inlineStr"/>
-      <c r="T483" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>20026</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>2.5in x 10in Carbon Filter</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>16.39</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>11.48</t>
+        </is>
+      </c>
       <c r="U483" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V483" t="inlineStr">
-        <is>
-          <t>0.311</t>
-        </is>
-      </c>
-      <c r="W483" t="inlineStr">
-        <is>
-          <t>Scraper 5in Ettore</t>
-        </is>
-      </c>
-      <c r="X483" t="inlineStr">
-        <is>
-          <t>46312</t>
-        </is>
-      </c>
-      <c r="Y483" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z483" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA483" t="inlineStr">
-        <is>
-          <t>0.298</t>
-        </is>
-      </c>
-      <c r="AB483" t="inlineStr">
-        <is>
-          <t>T-bar and Golden Glove Sleeve 10in Ettore</t>
-        </is>
-      </c>
-      <c r="AC483" t="inlineStr">
-        <is>
-          <t>JRACEN-GOLDEN-GLOVE-WASHER-COMPLETE-SLE</t>
-        </is>
-      </c>
-      <c r="AD483" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE483" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF483" t="inlineStr">
-        <is>
-          <t>0.287</t>
-        </is>
-      </c>
-      <c r="AG483" t="inlineStr">
-        <is>
-          <t>Blades ProPlus 06in Carbon Stl (25) Etto</t>
-        </is>
-      </c>
-      <c r="AH483" t="inlineStr">
-        <is>
-          <t>JRACEN-PRO-CONTOUR-STEEL-REPLACEMENT-BL</t>
-        </is>
-      </c>
-      <c r="AI483" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ483" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V483" t="inlineStr"/>
+      <c r="W483" t="inlineStr"/>
+      <c r="X483" t="inlineStr"/>
+      <c r="Y483" t="inlineStr"/>
+      <c r="Z483" t="inlineStr"/>
+      <c r="AA483" t="inlineStr"/>
+      <c r="AB483" t="inlineStr"/>
+      <c r="AC483" t="inlineStr"/>
+      <c r="AD483" t="inlineStr"/>
+      <c r="AE483" t="inlineStr"/>
+      <c r="AF483" t="inlineStr"/>
+      <c r="AG483" t="inlineStr"/>
+      <c r="AH483" t="inlineStr"/>
+      <c r="AI483" t="inlineStr"/>
+      <c r="AJ483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -69338,17 +68566,17 @@
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O499" t="inlineStr">
@@ -69356,41 +68584,41 @@
           <t>0.000</t>
         </is>
       </c>
-      <c r="P499" t="inlineStr"/>
-      <c r="Q499" t="inlineStr"/>
-      <c r="R499" t="inlineStr"/>
-      <c r="S499" t="inlineStr"/>
-      <c r="T499" t="inlineStr"/>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>20036</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>4 Inch Filter Wrench</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>13.67</t>
+        </is>
+      </c>
+      <c r="T499" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
       <c r="U499" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="V499" t="inlineStr">
-        <is>
-          <t>0.331</t>
-        </is>
-      </c>
-      <c r="W499" t="inlineStr">
-        <is>
-          <t>Blades 4in for HD Scraper (10) Ettore</t>
-        </is>
-      </c>
-      <c r="X499" t="inlineStr">
-        <is>
-          <t>20291</t>
-        </is>
-      </c>
-      <c r="Y499" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z499" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V499" t="inlineStr"/>
+      <c r="W499" t="inlineStr"/>
+      <c r="X499" t="inlineStr"/>
+      <c r="Y499" t="inlineStr"/>
+      <c r="Z499" t="inlineStr"/>
       <c r="AA499" t="inlineStr"/>
       <c r="AB499" t="inlineStr"/>
       <c r="AC499" t="inlineStr"/>
@@ -70042,12 +69270,12 @@
       </c>
       <c r="N504" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>0.522</t>
         </is>
       </c>
       <c r="O504" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P504" t="inlineStr"/>
@@ -70057,84 +69285,44 @@
       <c r="T504" t="inlineStr"/>
       <c r="U504" t="inlineStr">
         <is>
-          <t>1 shared tokens</t>
+          <t>2 shared tokens</t>
         </is>
       </c>
       <c r="V504" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>0.522</t>
         </is>
       </c>
       <c r="W504" t="inlineStr">
         <is>
-          <t>POLY 3/4" BULKHEAD FITTING</t>
+          <t>1/2' PTF Tee Fitting</t>
         </is>
       </c>
       <c r="X504" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>62004</t>
         </is>
       </c>
       <c r="Y504" t="inlineStr">
         <is>
-          <t>Barrens</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z504" t="inlineStr">
         <is>
-          <t>1 shared tokens</t>
-        </is>
-      </c>
-      <c r="AA504" t="inlineStr">
-        <is>
-          <t>0.428</t>
-        </is>
-      </c>
-      <c r="AB504" t="inlineStr">
-        <is>
-          <t>3/4" PVC Tee</t>
-        </is>
-      </c>
-      <c r="AC504" t="inlineStr">
-        <is>
-          <t>405-007</t>
-        </is>
-      </c>
-      <c r="AD504" t="inlineStr">
-        <is>
-          <t>MPWSR</t>
-        </is>
-      </c>
-      <c r="AE504" t="inlineStr">
-        <is>
-          <t>1 shared tokens</t>
-        </is>
-      </c>
-      <c r="AF504" t="inlineStr">
-        <is>
-          <t>0.410</t>
-        </is>
-      </c>
-      <c r="AG504" t="inlineStr">
-        <is>
-          <t>POLY 1" BULKHEAD FITTING</t>
-        </is>
-      </c>
-      <c r="AH504" t="inlineStr">
-        <is>
-          <t>4491</t>
-        </is>
-      </c>
-      <c r="AI504" t="inlineStr">
-        <is>
-          <t>Barrens</t>
-        </is>
-      </c>
-      <c r="AJ504" t="inlineStr">
-        <is>
-          <t>1 shared tokens</t>
-        </is>
-      </c>
+          <t>2 shared tokens</t>
+        </is>
+      </c>
+      <c r="AA504" t="inlineStr"/>
+      <c r="AB504" t="inlineStr"/>
+      <c r="AC504" t="inlineStr"/>
+      <c r="AD504" t="inlineStr"/>
+      <c r="AE504" t="inlineStr"/>
+      <c r="AF504" t="inlineStr"/>
+      <c r="AG504" t="inlineStr"/>
+      <c r="AH504" t="inlineStr"/>
+      <c r="AI504" t="inlineStr"/>
+      <c r="AJ504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -70512,12 +69700,12 @@
       </c>
       <c r="N507" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.677</t>
         </is>
       </c>
       <c r="O507" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="P507" t="inlineStr"/>
@@ -70527,82 +69715,82 @@
       <c r="T507" t="inlineStr"/>
       <c r="U507" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit, name contains match</t>
         </is>
       </c>
       <c r="V507" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.677</t>
         </is>
       </c>
       <c r="W507" t="inlineStr">
         <is>
-          <t>Pole Pro+ Snap-In Tip Nylon Ettore</t>
+          <t>Wood Cone Tip</t>
         </is>
       </c>
       <c r="X507" t="inlineStr">
         <is>
-          <t>JRACEN-PRO-POLE-TIP</t>
+          <t>T-WCT</t>
         </is>
       </c>
       <c r="Y507" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z507" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit, name contains match</t>
         </is>
       </c>
       <c r="AA507" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="AB507" t="inlineStr">
         <is>
-          <t>Auto Squeegee Scrubber Wood 8" Head, 25" overall</t>
+          <t>Tucker® ACME Tip</t>
         </is>
       </c>
       <c r="AC507" t="inlineStr">
         <is>
-          <t>59020</t>
+          <t>T-ACME-TIP-ALUMINUM</t>
         </is>
       </c>
       <c r="AD507" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>0.535</t>
         </is>
       </c>
       <c r="AG507" t="inlineStr">
         <is>
-          <t>Auto Squeegee Scrubber Wood 8" Head, 17" overall</t>
+          <t>Tucker® Euro Tip</t>
         </is>
       </c>
       <c r="AH507" t="inlineStr">
         <is>
-          <t>59816</t>
+          <t>T-EURO-TIP-PLASTIC</t>
         </is>
       </c>
       <c r="AI507" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AJ507" t="inlineStr">
         <is>
-          <t>1 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -72230,12 +71418,12 @@
       </c>
       <c r="N520" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="O520" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P520" t="inlineStr"/>
@@ -72245,84 +71433,44 @@
       <c r="T520" t="inlineStr"/>
       <c r="U520" t="inlineStr">
         <is>
-          <t>2 shared tokens</t>
+          <t>3 shared tokens</t>
         </is>
       </c>
       <c r="V520" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="W520" t="inlineStr">
         <is>
-          <t>5/8" Barb x 1/2" MNPT Brass Barb</t>
+          <t>3/8 barb x 1/2 male thread</t>
         </is>
       </c>
       <c r="X520" t="inlineStr">
         <is>
-          <t>32020</t>
+          <t>63001</t>
         </is>
       </c>
       <c r="Y520" t="inlineStr">
         <is>
-          <t>MPWSR</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z520" t="inlineStr">
         <is>
-          <t>2 shared tokens</t>
-        </is>
-      </c>
-      <c r="AA520" t="inlineStr">
-        <is>
-          <t>0.415</t>
-        </is>
-      </c>
-      <c r="AB520" t="inlineStr">
-        <is>
-          <t>1 1/4" Mpt x 1 1/2" Hose Barb</t>
-        </is>
-      </c>
-      <c r="AC520" t="inlineStr">
-        <is>
-          <t>HB125-150</t>
-        </is>
-      </c>
-      <c r="AD520" t="inlineStr">
-        <is>
-          <t>MPWSR</t>
-        </is>
-      </c>
-      <c r="AE520" t="inlineStr">
-        <is>
-          <t>2 shared tokens</t>
-        </is>
-      </c>
-      <c r="AF520" t="inlineStr">
-        <is>
-          <t>0.402</t>
-        </is>
-      </c>
-      <c r="AG520" t="inlineStr">
-        <is>
-          <t>Banjo Poly 2" Male Thread x 2" Hose Barb</t>
-        </is>
-      </c>
-      <c r="AH520" t="inlineStr">
-        <is>
-          <t>BHB200</t>
-        </is>
-      </c>
-      <c r="AI520" t="inlineStr">
-        <is>
-          <t>MPWSR</t>
-        </is>
-      </c>
-      <c r="AJ520" t="inlineStr">
-        <is>
-          <t>2 shared tokens</t>
-        </is>
-      </c>
+          <t>3 shared tokens</t>
+        </is>
+      </c>
+      <c r="AA520" t="inlineStr"/>
+      <c r="AB520" t="inlineStr"/>
+      <c r="AC520" t="inlineStr"/>
+      <c r="AD520" t="inlineStr"/>
+      <c r="AE520" t="inlineStr"/>
+      <c r="AF520" t="inlineStr"/>
+      <c r="AG520" t="inlineStr"/>
+      <c r="AH520" t="inlineStr"/>
+      <c r="AI520" t="inlineStr"/>
+      <c r="AJ520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -72992,109 +72140,69 @@
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>exact_sku</t>
         </is>
       </c>
       <c r="M526" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N526" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O526" t="inlineStr">
         <is>
-          <t>0.263</t>
-        </is>
-      </c>
-      <c r="P526" t="inlineStr"/>
-      <c r="Q526" t="inlineStr"/>
-      <c r="R526" t="inlineStr"/>
-      <c r="S526" t="inlineStr"/>
-      <c r="T526" t="inlineStr"/>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>62006</t>
+        </is>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>3/8 PTF x 1/4 PTF Reducer</t>
+        </is>
+      </c>
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="T526" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="U526" t="inlineStr">
         <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="V526" t="inlineStr">
-        <is>
-          <t>0.263</t>
-        </is>
-      </c>
-      <c r="W526" t="inlineStr">
-        <is>
-          <t>Elite Poly Duster</t>
-        </is>
-      </c>
-      <c r="X526" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="Y526" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z526" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="AA526" t="inlineStr">
-        <is>
-          <t>0.263</t>
-        </is>
-      </c>
-      <c r="AB526" t="inlineStr">
-        <is>
-          <t>Bucket 3 1/2 Gal Ettore Round - each</t>
-        </is>
-      </c>
-      <c r="AC526" t="inlineStr">
-        <is>
-          <t>82222</t>
-        </is>
-      </c>
-      <c r="AD526" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE526" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
-      <c r="AF526" t="inlineStr">
-        <is>
-          <t>0.261</t>
-        </is>
-      </c>
-      <c r="AG526" t="inlineStr">
-        <is>
-          <t>Bucket Super Compact w/Handle Ettore</t>
-        </is>
-      </c>
-      <c r="AH526" t="inlineStr">
-        <is>
-          <t>86000</t>
-        </is>
-      </c>
-      <c r="AI526" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ526" t="inlineStr">
-        <is>
-          <t>category fit</t>
-        </is>
-      </c>
+          <t>Sales SKU exactly matches catalog SKU or vendor code.</t>
+        </is>
+      </c>
+      <c r="V526" t="inlineStr"/>
+      <c r="W526" t="inlineStr"/>
+      <c r="X526" t="inlineStr"/>
+      <c r="Y526" t="inlineStr"/>
+      <c r="Z526" t="inlineStr"/>
+      <c r="AA526" t="inlineStr"/>
+      <c r="AB526" t="inlineStr"/>
+      <c r="AC526" t="inlineStr"/>
+      <c r="AD526" t="inlineStr"/>
+      <c r="AE526" t="inlineStr"/>
+      <c r="AF526" t="inlineStr"/>
+      <c r="AG526" t="inlineStr"/>
+      <c r="AH526" t="inlineStr"/>
+      <c r="AI526" t="inlineStr"/>
+      <c r="AJ526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -73630,12 +72738,12 @@
       </c>
       <c r="N530" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>0.644</t>
         </is>
       </c>
       <c r="O530" t="inlineStr">
         <is>
-          <t>0.480</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P530" t="inlineStr"/>
@@ -73645,84 +72753,44 @@
       <c r="T530" t="inlineStr"/>
       <c r="U530" t="inlineStr">
         <is>
-          <t>2 shared tokens</t>
+          <t>3 shared tokens</t>
         </is>
       </c>
       <c r="V530" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>0.644</t>
         </is>
       </c>
       <c r="W530" t="inlineStr">
         <is>
-          <t>POLY 1/2" BULKHEAD FITTING</t>
+          <t>1/2' PTF Tee Fitting</t>
         </is>
       </c>
       <c r="X530" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>62004</t>
         </is>
       </c>
       <c r="Y530" t="inlineStr">
         <is>
-          <t>Barrens</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="Z530" t="inlineStr">
         <is>
-          <t>2 shared tokens</t>
-        </is>
-      </c>
-      <c r="AA530" t="inlineStr">
-        <is>
-          <t>0.480</t>
-        </is>
-      </c>
-      <c r="AB530" t="inlineStr">
-        <is>
-          <t>1/2" PVC Tee</t>
-        </is>
-      </c>
-      <c r="AC530" t="inlineStr">
-        <is>
-          <t>405-005</t>
-        </is>
-      </c>
-      <c r="AD530" t="inlineStr">
-        <is>
-          <t>MPWSR</t>
-        </is>
-      </c>
-      <c r="AE530" t="inlineStr">
-        <is>
-          <t>2 shared tokens</t>
-        </is>
-      </c>
-      <c r="AF530" t="inlineStr">
-        <is>
-          <t>0.473</t>
-        </is>
-      </c>
-      <c r="AG530" t="inlineStr">
-        <is>
-          <t>POLY 1 1/2" BULKHEAD FITTING</t>
-        </is>
-      </c>
-      <c r="AH530" t="inlineStr">
-        <is>
-          <t>4209</t>
-        </is>
-      </c>
-      <c r="AI530" t="inlineStr">
-        <is>
-          <t>Barrens</t>
-        </is>
-      </c>
-      <c r="AJ530" t="inlineStr">
-        <is>
-          <t>2 shared tokens</t>
-        </is>
-      </c>
+          <t>3 shared tokens</t>
+        </is>
+      </c>
+      <c r="AA530" t="inlineStr"/>
+      <c r="AB530" t="inlineStr"/>
+      <c r="AC530" t="inlineStr"/>
+      <c r="AD530" t="inlineStr"/>
+      <c r="AE530" t="inlineStr"/>
+      <c r="AF530" t="inlineStr"/>
+      <c r="AG530" t="inlineStr"/>
+      <c r="AH530" t="inlineStr"/>
+      <c r="AI530" t="inlineStr"/>
+      <c r="AJ530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -74065,7 +73133,7 @@
       </c>
       <c r="O533" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>0.300</t>
         </is>
       </c>
       <c r="P533" t="inlineStr"/>
@@ -74097,22 +73165,22 @@
       <c r="Z533" t="inlineStr"/>
       <c r="AA533" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>0.300</t>
         </is>
       </c>
       <c r="AB533" t="inlineStr">
         <is>
-          <t>CAMLOCK, ALUM 3" DP</t>
+          <t>Lubricant Packet</t>
         </is>
       </c>
       <c r="AC533" t="inlineStr">
         <is>
-          <t>90.397.300</t>
+          <t>T-LUBE</t>
         </is>
       </c>
       <c r="AD533" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="AE533" t="inlineStr"/>
@@ -74123,12 +73191,12 @@
       </c>
       <c r="AG533" t="inlineStr">
         <is>
-          <t>CAMLOCK, ALUM 2" DC</t>
+          <t>CAMLOCK, ALUM 3" DP</t>
         </is>
       </c>
       <c r="AH533" t="inlineStr">
         <is>
-          <t>90.396.200</t>
+          <t>90.397.300</t>
         </is>
       </c>
       <c r="AI533" t="inlineStr">

--- a/outputs/sales_item_match_audit.xlsx
+++ b/outputs/sales_item_match_audit.xlsx
@@ -23806,12 +23806,12 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="P180" t="inlineStr"/>
@@ -23821,17 +23821,17 @@
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
+          <t>1 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>T-Shaped Rubber, 18"</t>
         </is>
       </c>
       <c r="X180" t="inlineStr">
@@ -23846,19 +23846,59 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr"/>
-      <c r="AB180" t="inlineStr"/>
-      <c r="AC180" t="inlineStr"/>
-      <c r="AD180" t="inlineStr"/>
-      <c r="AE180" t="inlineStr"/>
-      <c r="AF180" t="inlineStr"/>
-      <c r="AG180" t="inlineStr"/>
-      <c r="AH180" t="inlineStr"/>
-      <c r="AI180" t="inlineStr"/>
-      <c r="AJ180" t="inlineStr"/>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>0.419</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>Ettore Sleeve Pro+ Microfiber 18 inch</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>40018</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>0.415</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>Ettore Squeegee Complete 18</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>JRACEN-MASTER-BRASS-SQUEEGEES-COMPLET-3</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -25779,7 +25819,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.426</t>
         </is>
       </c>
       <c r="P194" t="inlineStr"/>
@@ -25819,17 +25859,17 @@
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.426</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>Ettore T-Bar ProGrip 18 inch</t>
         </is>
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>JRACEN-T-SHAPED-RUBBER-18</t>
+          <t>JRACEN-PRO-GRIP-T-BAR-18</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr">
@@ -25839,32 +25879,32 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>0.419</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>Ettore Channel Classic Aluminum 18 inch</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>1918</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
           <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>0.426</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>Ettore T-Bar ProGrip 18 inch</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>JRACEN-PRO-GRIP-T-BAR-18</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -28972,12 +29012,12 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.371</t>
         </is>
       </c>
       <c r="P217" t="inlineStr"/>
@@ -28987,17 +29027,17 @@
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
+          <t>1 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 30 inch</t>
+          <t>T-Shaped Rubber, 30"</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
@@ -29012,19 +29052,59 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA217" t="inlineStr"/>
-      <c r="AB217" t="inlineStr"/>
-      <c r="AC217" t="inlineStr"/>
-      <c r="AD217" t="inlineStr"/>
-      <c r="AE217" t="inlineStr"/>
-      <c r="AF217" t="inlineStr"/>
-      <c r="AG217" t="inlineStr"/>
-      <c r="AH217" t="inlineStr"/>
-      <c r="AI217" t="inlineStr"/>
-      <c r="AJ217" t="inlineStr"/>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>0.371</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>Aluminum Floor Squeegees, Straight, 30"</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>55030</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>0.361</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>Ettore Super Channel Aluminum 30 inch</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>11040</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -31999,7 +32079,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.312</t>
         </is>
       </c>
       <c r="P238" t="inlineStr"/>
@@ -32039,17 +32119,17 @@
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.312</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>T-Shaped Rubber, 36"</t>
         </is>
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>JRACEN-T-SHAPED-RUBBER-18</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="AD238" t="inlineStr">
@@ -32059,22 +32139,22 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
+          <t>1 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.312</t>
         </is>
       </c>
       <c r="AG238" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 36 inch</t>
+          <t>T-Shaped Rubber, 30"</t>
         </is>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="AI238" t="inlineStr">
@@ -32084,7 +32164,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
+          <t>1 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -34275,7 +34355,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>0.231</t>
         </is>
       </c>
       <c r="P254" t="inlineStr"/>
@@ -34315,17 +34395,17 @@
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>0.231</t>
         </is>
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>Sorbo Channel Ultralight w/End Clip 14 inch [Case 36]</t>
         </is>
       </c>
       <c r="AC254" t="inlineStr">
         <is>
-          <t>JRACEN-T-SHAPED-RUBBER-18</t>
+          <t>JRACEN-MASTER-BRASS-CHANNELS-WITH-RUB-8</t>
         </is>
       </c>
       <c r="AD254" t="inlineStr">
@@ -34340,17 +34420,17 @@
       </c>
       <c r="AF254" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0.231</t>
         </is>
       </c>
       <c r="AG254" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 36 inch</t>
+          <t>Sorbo Channel Ultralight w/End Clip 06 inch [Case 36]</t>
         </is>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>JRACEN-MASTER-BRASS-CHANNELS-WITH-RUB-6</t>
         </is>
       </c>
       <c r="AI254" t="inlineStr">
@@ -34432,12 +34512,12 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>0.420</t>
+          <t>0.310</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>0.420</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="P255" t="inlineStr"/>
@@ -34447,22 +34527,22 @@
       <c r="T255" t="inlineStr"/>
       <c r="U255" t="inlineStr">
         <is>
-          <t>3 shared tokens, category fit</t>
+          <t>1 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>0.420</t>
+          <t>0.310</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 36 inch</t>
+          <t>Ettore Pole Replacement Grip 3rd</t>
         </is>
       </c>
       <c r="X255" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>JRACEN-REPLACEMENT-GRIPS-3-SEC</t>
         </is>
       </c>
       <c r="Y255" t="inlineStr">
@@ -34472,22 +34552,22 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>3 shared tokens, category fit</t>
+          <t>1 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>0.420</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 30 inch</t>
+          <t>Ettore Rubber Master Replacement Dozen 08 inch</t>
         </is>
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>JRACEN-MASTER-RUBBER-8</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -34497,22 +34577,22 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>3 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
         <is>
-          <t>0.420</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="AG255" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 24 inch</t>
+          <t>Ettore Rubber Master Replacement Dozen 06 inch</t>
         </is>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>JRACEN-MASTER-RUBBER-6</t>
         </is>
       </c>
       <c r="AI255" t="inlineStr">
@@ -34522,7 +34602,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>3 shared tokens, category fit</t>
+          <t>2 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -35588,12 +35668,12 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.344</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>0.337</t>
         </is>
       </c>
       <c r="P263" t="inlineStr"/>
@@ -35608,67 +35688,67 @@
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.344</t>
         </is>
       </c>
       <c r="W263" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 22 inch</t>
+          <t>Ettore Rubber Master Replacement Gross 22 inch [Case 144]</t>
         </is>
       </c>
       <c r="X263" t="inlineStr">
         <is>
+          <t>JRACEN-MASTER-RUBBER-22-CASE-144</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>2 shared tokens</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>0.337</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>Ettore Rubber Master Replacement Dozen 22 inch [Case 12]</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>2 shared tokens</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>0.321</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>T-Shaped Rubber, 22"</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
           <t>JRACEN-T-SHAPED-RUBBER-22</t>
-        </is>
-      </c>
-      <c r="Y263" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>2 shared tokens</t>
-        </is>
-      </c>
-      <c r="AA263" t="inlineStr">
-        <is>
-          <t>0.344</t>
-        </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>Ettore Rubber Master Replacement Gross 22 inch [Case 144]</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>JRACEN-MASTER-RUBBER-22-CASE-144</t>
-        </is>
-      </c>
-      <c r="AD263" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE263" t="inlineStr">
-        <is>
-          <t>2 shared tokens</t>
-        </is>
-      </c>
-      <c r="AF263" t="inlineStr">
-        <is>
-          <t>0.337</t>
-        </is>
-      </c>
-      <c r="AG263" t="inlineStr">
-        <is>
-          <t>Ettore Rubber Master Replacement Dozen 22 inch [Case 12]</t>
-        </is>
-      </c>
-      <c r="AH263" t="inlineStr">
-        <is>
-          <t>1438</t>
         </is>
       </c>
       <c r="AI263" t="inlineStr">
@@ -36940,12 +37020,12 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P273" t="inlineStr"/>
@@ -36960,17 +37040,17 @@
       </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="W273" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 14 inch</t>
+          <t>Sorbo Channel Ultralight w/End Clip 14 inch [Case 36]</t>
         </is>
       </c>
       <c r="X273" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>JRACEN-MASTER-BRASS-CHANNELS-WITH-RUB-8</t>
         </is>
       </c>
       <c r="Y273" t="inlineStr">
@@ -36983,31 +37063,11 @@
           <t>2 shared tokens, category fit</t>
         </is>
       </c>
-      <c r="AA273" t="inlineStr">
-        <is>
-          <t>0.329</t>
-        </is>
-      </c>
-      <c r="AB273" t="inlineStr">
-        <is>
-          <t>Sorbo Channel Ultralight w/End Clip 14 inch [Case 36]</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>JRACEN-MASTER-BRASS-CHANNELS-WITH-RUB-8</t>
-        </is>
-      </c>
-      <c r="AD273" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE273" t="inlineStr">
-        <is>
-          <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
+      <c r="AA273" t="inlineStr"/>
+      <c r="AB273" t="inlineStr"/>
+      <c r="AC273" t="inlineStr"/>
+      <c r="AD273" t="inlineStr"/>
+      <c r="AE273" t="inlineStr"/>
       <c r="AF273" t="inlineStr"/>
       <c r="AG273" t="inlineStr"/>
       <c r="AH273" t="inlineStr"/>
@@ -41995,7 +42055,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.312</t>
         </is>
       </c>
       <c r="P308" t="inlineStr"/>
@@ -42035,17 +42095,17 @@
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.312</t>
         </is>
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>T-Shaped Rubber, 36"</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
         <is>
-          <t>JRACEN-T-SHAPED-RUBBER-18</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="AD308" t="inlineStr">
@@ -42055,22 +42115,22 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
+          <t>1 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.312</t>
         </is>
       </c>
       <c r="AG308" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 36 inch</t>
+          <t>T-Shaped Rubber, 30"</t>
         </is>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="AI308" t="inlineStr">
@@ -42080,7 +42140,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
+          <t>1 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -44171,7 +44231,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.386</t>
         </is>
       </c>
       <c r="P324" t="inlineStr"/>
@@ -44211,42 +44271,42 @@
       </c>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.386</t>
         </is>
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 24 inch</t>
+          <t>Super Channel 14"</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
         <is>
+          <t>JRACEN-SUPER-CHANNEL-14</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AF324" t="inlineStr">
+        <is>
+          <t>0.373</t>
+        </is>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>T-Shaped Rubber, 24"</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
           <t>1512</t>
-        </is>
-      </c>
-      <c r="AD324" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE324" t="inlineStr">
-        <is>
-          <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF324" t="inlineStr">
-        <is>
-          <t>0.386</t>
-        </is>
-      </c>
-      <c r="AG324" t="inlineStr">
-        <is>
-          <t>Super Channel 14"</t>
-        </is>
-      </c>
-      <c r="AH324" t="inlineStr">
-        <is>
-          <t>JRACEN-SUPER-CHANNEL-14</t>
         </is>
       </c>
       <c r="AI324" t="inlineStr">
@@ -47740,12 +47800,12 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>0.550</t>
+          <t>0.484</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="P349" t="inlineStr"/>
@@ -47760,17 +47820,17 @@
       </c>
       <c r="V349" t="inlineStr">
         <is>
-          <t>0.550</t>
+          <t>0.484</t>
         </is>
       </c>
       <c r="W349" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>Ettore Rubber Master Replacement Dozen 18 inch [Case 12]</t>
         </is>
       </c>
       <c r="X349" t="inlineStr">
         <is>
-          <t>JRACEN-T-SHAPED-RUBBER-18</t>
+          <t>JRACEN-MASTER-RUBBER-18-CASE-12</t>
         </is>
       </c>
       <c r="Y349" t="inlineStr">
@@ -47785,17 +47845,17 @@
       </c>
       <c r="AA349" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>Ettore Rubber Master Replacement Dozen 18 inch [Case 12]</t>
+          <t>Ettore Rubber Master Replacement Dozen 12 inch [Case 12]</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
         <is>
-          <t>JRACEN-MASTER-RUBBER-18-CASE-12</t>
+          <t>JRACEN-MASTER-RUBBER-12-CASE-12</t>
         </is>
       </c>
       <c r="AD349" t="inlineStr">
@@ -47805,22 +47865,22 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>4 shared tokens, category fit</t>
+          <t>3 shared tokens, category fit</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.397</t>
         </is>
       </c>
       <c r="AG349" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 24 inch</t>
+          <t>Ettore Rubber Master Replacement Gross 12 inch [Case 144]</t>
         </is>
       </c>
       <c r="AH349" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>JRACEN-MASTER-RUBBER-12-CASE-144</t>
         </is>
       </c>
       <c r="AI349" t="inlineStr">
@@ -50988,12 +51048,12 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>0.300</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="P373" t="inlineStr"/>
@@ -51008,17 +51068,17 @@
       </c>
       <c r="V373" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>0.300</t>
         </is>
       </c>
       <c r="W373" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>Ettore Sleeve Dura 22 inch</t>
         </is>
       </c>
       <c r="X373" t="inlineStr">
         <is>
-          <t>JRACEN-T-SHAPED-RUBBER-18</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="Y373" t="inlineStr">
@@ -51033,17 +51093,17 @@
       </c>
       <c r="AA373" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 22 inch</t>
+          <t>Ettore Sleeve Dura 18 inch</t>
         </is>
       </c>
       <c r="AC373" t="inlineStr">
         <is>
-          <t>JRACEN-T-SHAPED-RUBBER-22</t>
+          <t>JRACEN-DURA-2-SLEEVE-18</t>
         </is>
       </c>
       <c r="AD373" t="inlineStr">
@@ -51058,17 +51118,17 @@
       </c>
       <c r="AF373" t="inlineStr">
         <is>
-          <t>0.300</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="AG373" t="inlineStr">
         <is>
-          <t>Ettore Sleeve Dura 22 inch</t>
+          <t>Ettore Sleeve Dura 14 inch</t>
         </is>
       </c>
       <c r="AH373" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="AI373" t="inlineStr">
@@ -52434,7 +52494,7 @@
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>0.463</t>
         </is>
       </c>
       <c r="O384" t="inlineStr">
@@ -52454,12 +52514,12 @@
       </c>
       <c r="V384" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>0.463</t>
         </is>
       </c>
       <c r="W384" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>T-Shaped Rubber, 18"</t>
         </is>
       </c>
       <c r="X384" t="inlineStr">
@@ -55948,12 +56008,12 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>0.377</t>
         </is>
       </c>
       <c r="P409" t="inlineStr"/>
@@ -55968,67 +56028,67 @@
       </c>
       <c r="V409" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="W409" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 14 inch</t>
+          <t>Ettore Rubber Master Replacement Gross 14 inch [Case 144]</t>
         </is>
       </c>
       <c r="X409" t="inlineStr">
         <is>
+          <t>JRACEN-MASTER-RUBBER-14-CASE-144</t>
+        </is>
+      </c>
+      <c r="Y409" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="Z409" t="inlineStr">
+        <is>
+          <t>2 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>0.377</t>
+        </is>
+      </c>
+      <c r="AB409" t="inlineStr">
+        <is>
+          <t>Ettore Rubber Master Replacement Dozen 14 inch [Case 12]</t>
+        </is>
+      </c>
+      <c r="AC409" t="inlineStr">
+        <is>
+          <t>JRACEN-MASTER-RUBBER-14-CASE-12</t>
+        </is>
+      </c>
+      <c r="AD409" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AE409" t="inlineStr">
+        <is>
+          <t>2 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AF409" t="inlineStr">
+        <is>
+          <t>0.361</t>
+        </is>
+      </c>
+      <c r="AG409" t="inlineStr">
+        <is>
+          <t>T-Shaped Rubber, 14"</t>
+        </is>
+      </c>
+      <c r="AH409" t="inlineStr">
+        <is>
           <t>1497</t>
-        </is>
-      </c>
-      <c r="Y409" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="Z409" t="inlineStr">
-        <is>
-          <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA409" t="inlineStr">
-        <is>
-          <t>0.384</t>
-        </is>
-      </c>
-      <c r="AB409" t="inlineStr">
-        <is>
-          <t>Ettore Rubber Master Replacement Gross 14 inch [Case 144]</t>
-        </is>
-      </c>
-      <c r="AC409" t="inlineStr">
-        <is>
-          <t>JRACEN-MASTER-RUBBER-14-CASE-144</t>
-        </is>
-      </c>
-      <c r="AD409" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AE409" t="inlineStr">
-        <is>
-          <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF409" t="inlineStr">
-        <is>
-          <t>0.377</t>
-        </is>
-      </c>
-      <c r="AG409" t="inlineStr">
-        <is>
-          <t>Ettore Rubber Master Replacement Dozen 14 inch [Case 12]</t>
-        </is>
-      </c>
-      <c r="AH409" t="inlineStr">
-        <is>
-          <t>JRACEN-MASTER-RUBBER-14-CASE-12</t>
         </is>
       </c>
       <c r="AI409" t="inlineStr">
@@ -57621,7 +57681,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>0.300</t>
         </is>
       </c>
       <c r="P421" t="inlineStr"/>
@@ -57661,17 +57721,17 @@
       </c>
       <c r="AA421" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>0.300</t>
         </is>
       </c>
       <c r="AB421" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>Ettore Sleeve Dura 14 inch</t>
         </is>
       </c>
       <c r="AC421" t="inlineStr">
         <is>
-          <t>JRACEN-T-SHAPED-RUBBER-18</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="AD421" t="inlineStr">
@@ -57686,17 +57746,17 @@
       </c>
       <c r="AF421" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.295</t>
         </is>
       </c>
       <c r="AG421" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 14 inch</t>
+          <t>Ettore Sleeve Mighty 14 inch</t>
         </is>
       </c>
       <c r="AH421" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>52014</t>
         </is>
       </c>
       <c r="AI421" t="inlineStr">
@@ -63054,12 +63114,12 @@
       </c>
       <c r="N460" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.396</t>
         </is>
       </c>
       <c r="P460" t="inlineStr"/>
@@ -63069,17 +63129,17 @@
       <c r="T460" t="inlineStr"/>
       <c r="U460" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
+          <t>1 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V460" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="W460" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 24 inch</t>
+          <t>T-Shaped Rubber, 24"</t>
         </is>
       </c>
       <c r="X460" t="inlineStr">
@@ -63094,19 +63154,59 @@
       </c>
       <c r="Z460" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA460" t="inlineStr"/>
-      <c r="AB460" t="inlineStr"/>
-      <c r="AC460" t="inlineStr"/>
-      <c r="AD460" t="inlineStr"/>
-      <c r="AE460" t="inlineStr"/>
-      <c r="AF460" t="inlineStr"/>
-      <c r="AG460" t="inlineStr"/>
-      <c r="AH460" t="inlineStr"/>
-      <c r="AI460" t="inlineStr"/>
-      <c r="AJ460" t="inlineStr"/>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AA460" t="inlineStr">
+        <is>
+          <t>0.396</t>
+        </is>
+      </c>
+      <c r="AB460" t="inlineStr">
+        <is>
+          <t>Industrial Floor Squeege, Curved, 24"</t>
+        </is>
+      </c>
+      <c r="AC460" t="inlineStr">
+        <is>
+          <t>54524</t>
+        </is>
+      </c>
+      <c r="AD460" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AE460" t="inlineStr">
+        <is>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AF460" t="inlineStr">
+        <is>
+          <t>0.390</t>
+        </is>
+      </c>
+      <c r="AG460" t="inlineStr">
+        <is>
+          <t>Industrial Floor Squeege, Straight, 24"</t>
+        </is>
+      </c>
+      <c r="AH460" t="inlineStr">
+        <is>
+          <t>54024</t>
+        </is>
+      </c>
+      <c r="AI460" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AJ460" t="inlineStr">
+        <is>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -63628,17 +63728,17 @@
       </c>
       <c r="AF464" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="AG464" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>Ettore T-Bar Taper Plastic 18 inch</t>
         </is>
       </c>
       <c r="AH464" t="inlineStr">
         <is>
-          <t>JRACEN-T-SHAPED-RUBBER-18</t>
+          <t>JRACEN-TAPER-T-BAR-T-BAR-18</t>
         </is>
       </c>
       <c r="AI464" t="inlineStr">
@@ -64624,12 +64724,12 @@
       </c>
       <c r="N471" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="P471" t="inlineStr"/>
@@ -64644,17 +64744,17 @@
       </c>
       <c r="V471" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="W471" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>Sorbo Channel Ultralight w/End Clip 14 inch [Case 36]</t>
         </is>
       </c>
       <c r="X471" t="inlineStr">
         <is>
-          <t>JRACEN-T-SHAPED-RUBBER-18</t>
+          <t>JRACEN-MASTER-BRASS-CHANNELS-WITH-RUB-8</t>
         </is>
       </c>
       <c r="Y471" t="inlineStr">
@@ -64669,17 +64769,17 @@
       </c>
       <c r="AA471" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="AB471" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 36 inch</t>
+          <t>Sorbo Channel Ultralight w/End Clip 06 inch [Case 36]</t>
         </is>
       </c>
       <c r="AC471" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>JRACEN-MASTER-BRASS-CHANNELS-WITH-RUB-6</t>
         </is>
       </c>
       <c r="AD471" t="inlineStr">
@@ -64692,31 +64792,11 @@
           <t>1 shared tokens, category fit</t>
         </is>
       </c>
-      <c r="AF471" t="inlineStr">
-        <is>
-          <t>0.239</t>
-        </is>
-      </c>
-      <c r="AG471" t="inlineStr">
-        <is>
-          <t>Sorbo Replacement Rubber Dozen 30 inch</t>
-        </is>
-      </c>
-      <c r="AH471" t="inlineStr">
-        <is>
-          <t>1518</t>
-        </is>
-      </c>
-      <c r="AI471" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ471" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+      <c r="AF471" t="inlineStr"/>
+      <c r="AG471" t="inlineStr"/>
+      <c r="AH471" t="inlineStr"/>
+      <c r="AI471" t="inlineStr"/>
+      <c r="AJ471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -64901,7 +64981,7 @@
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.426</t>
         </is>
       </c>
       <c r="P473" t="inlineStr"/>
@@ -64941,17 +65021,17 @@
       </c>
       <c r="AA473" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.426</t>
         </is>
       </c>
       <c r="AB473" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>Ettore T-Bar ProGrip 18 inch</t>
         </is>
       </c>
       <c r="AC473" t="inlineStr">
         <is>
-          <t>JRACEN-T-SHAPED-RUBBER-18</t>
+          <t>JRACEN-PRO-GRIP-T-BAR-18</t>
         </is>
       </c>
       <c r="AD473" t="inlineStr">
@@ -64961,32 +65041,32 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AF473" t="inlineStr">
+        <is>
+          <t>0.419</t>
+        </is>
+      </c>
+      <c r="AG473" t="inlineStr">
+        <is>
+          <t>Ettore Channel Classic Aluminum 18 inch</t>
+        </is>
+      </c>
+      <c r="AH473" t="inlineStr">
+        <is>
+          <t>1918</t>
+        </is>
+      </c>
+      <c r="AI473" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AJ473" t="inlineStr">
+        <is>
           <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AF473" t="inlineStr">
-        <is>
-          <t>0.426</t>
-        </is>
-      </c>
-      <c r="AG473" t="inlineStr">
-        <is>
-          <t>Ettore T-Bar ProGrip 18 inch</t>
-        </is>
-      </c>
-      <c r="AH473" t="inlineStr">
-        <is>
-          <t>JRACEN-PRO-GRIP-T-BAR-18</t>
-        </is>
-      </c>
-      <c r="AI473" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ473" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
         </is>
       </c>
     </row>
@@ -65054,12 +65134,12 @@
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.396</t>
         </is>
       </c>
       <c r="P474" t="inlineStr"/>
@@ -65069,17 +65149,17 @@
       <c r="T474" t="inlineStr"/>
       <c r="U474" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
+          <t>1 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V474" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="W474" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 24 inch</t>
+          <t>T-Shaped Rubber, 24"</t>
         </is>
       </c>
       <c r="X474" t="inlineStr">
@@ -65094,19 +65174,59 @@
       </c>
       <c r="Z474" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA474" t="inlineStr"/>
-      <c r="AB474" t="inlineStr"/>
-      <c r="AC474" t="inlineStr"/>
-      <c r="AD474" t="inlineStr"/>
-      <c r="AE474" t="inlineStr"/>
-      <c r="AF474" t="inlineStr"/>
-      <c r="AG474" t="inlineStr"/>
-      <c r="AH474" t="inlineStr"/>
-      <c r="AI474" t="inlineStr"/>
-      <c r="AJ474" t="inlineStr"/>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AA474" t="inlineStr">
+        <is>
+          <t>0.396</t>
+        </is>
+      </c>
+      <c r="AB474" t="inlineStr">
+        <is>
+          <t>Industrial Floor Squeege, Curved, 24"</t>
+        </is>
+      </c>
+      <c r="AC474" t="inlineStr">
+        <is>
+          <t>54524</t>
+        </is>
+      </c>
+      <c r="AD474" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AE474" t="inlineStr">
+        <is>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AF474" t="inlineStr">
+        <is>
+          <t>0.390</t>
+        </is>
+      </c>
+      <c r="AG474" t="inlineStr">
+        <is>
+          <t>Industrial Floor Squeege, Straight, 24"</t>
+        </is>
+      </c>
+      <c r="AH474" t="inlineStr">
+        <is>
+          <t>54024</t>
+        </is>
+      </c>
+      <c r="AI474" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AJ474" t="inlineStr">
+        <is>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -65870,12 +65990,12 @@
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="P480" t="inlineStr"/>
@@ -65885,17 +66005,17 @@
       <c r="T480" t="inlineStr"/>
       <c r="U480" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
+          <t>1 shared tokens, category fit</t>
         </is>
       </c>
       <c r="V480" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="W480" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>T-Shaped Rubber, 18"</t>
         </is>
       </c>
       <c r="X480" t="inlineStr">
@@ -65910,19 +66030,59 @@
       </c>
       <c r="Z480" t="inlineStr">
         <is>
-          <t>2 shared tokens, category fit</t>
-        </is>
-      </c>
-      <c r="AA480" t="inlineStr"/>
-      <c r="AB480" t="inlineStr"/>
-      <c r="AC480" t="inlineStr"/>
-      <c r="AD480" t="inlineStr"/>
-      <c r="AE480" t="inlineStr"/>
-      <c r="AF480" t="inlineStr"/>
-      <c r="AG480" t="inlineStr"/>
-      <c r="AH480" t="inlineStr"/>
-      <c r="AI480" t="inlineStr"/>
-      <c r="AJ480" t="inlineStr"/>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AA480" t="inlineStr">
+        <is>
+          <t>0.419</t>
+        </is>
+      </c>
+      <c r="AB480" t="inlineStr">
+        <is>
+          <t>Ettore Sleeve Pro+ Microfiber 18 inch</t>
+        </is>
+      </c>
+      <c r="AC480" t="inlineStr">
+        <is>
+          <t>40018</t>
+        </is>
+      </c>
+      <c r="AD480" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AE480" t="inlineStr">
+        <is>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
+      <c r="AF480" t="inlineStr">
+        <is>
+          <t>0.415</t>
+        </is>
+      </c>
+      <c r="AG480" t="inlineStr">
+        <is>
+          <t>Ettore Squeegee Complete 18</t>
+        </is>
+      </c>
+      <c r="AH480" t="inlineStr">
+        <is>
+          <t>JRACEN-MASTER-BRASS-SQUEEGEES-COMPLET-3</t>
+        </is>
+      </c>
+      <c r="AI480" t="inlineStr">
+        <is>
+          <t>JRacenstein</t>
+        </is>
+      </c>
+      <c r="AJ480" t="inlineStr">
+        <is>
+          <t>1 shared tokens, category fit</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -68265,7 +68425,7 @@
       </c>
       <c r="O497" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="P497" t="inlineStr"/>
@@ -68305,17 +68465,17 @@
       </c>
       <c r="AA497" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="AB497" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>Cover for 06in Super Scraper</t>
         </is>
       </c>
       <c r="AC497" t="inlineStr">
         <is>
-          <t>JRACEN-T-SHAPED-RUBBER-18</t>
+          <t>JRACEN-HEAVY-DUTY-SUPER-SCRAPER-COVER-6</t>
         </is>
       </c>
       <c r="AD497" t="inlineStr">
@@ -68330,17 +68490,17 @@
       </c>
       <c r="AF497" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="AG497" t="inlineStr">
         <is>
-          <t>Cover for 06in Super Scraper</t>
+          <t>Ettore Sleeve Dura 22 inch</t>
         </is>
       </c>
       <c r="AH497" t="inlineStr">
         <is>
-          <t>JRACEN-HEAVY-DUTY-SUPER-SCRAPER-COVER-6</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="AI497" t="inlineStr">
@@ -69542,12 +69702,12 @@
       </c>
       <c r="N506" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="O506" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="P506" t="inlineStr"/>
@@ -69562,17 +69722,17 @@
       </c>
       <c r="V506" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="W506" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Gross 18 inch</t>
+          <t>Sorbo Channel Ultralight w/End Clip 14 inch [Case 36]</t>
         </is>
       </c>
       <c r="X506" t="inlineStr">
         <is>
-          <t>JRACEN-T-SHAPED-RUBBER-18</t>
+          <t>JRACEN-MASTER-BRASS-CHANNELS-WITH-RUB-8</t>
         </is>
       </c>
       <c r="Y506" t="inlineStr">
@@ -69587,17 +69747,17 @@
       </c>
       <c r="AA506" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="AB506" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 36 inch</t>
+          <t>Sorbo Channel Ultralight w/End Clip 06 inch [Case 36]</t>
         </is>
       </c>
       <c r="AC506" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>JRACEN-MASTER-BRASS-CHANNELS-WITH-RUB-6</t>
         </is>
       </c>
       <c r="AD506" t="inlineStr">
@@ -69610,31 +69770,11 @@
           <t>1 shared tokens, category fit</t>
         </is>
       </c>
-      <c r="AF506" t="inlineStr">
-        <is>
-          <t>0.239</t>
-        </is>
-      </c>
-      <c r="AG506" t="inlineStr">
-        <is>
-          <t>Sorbo Replacement Rubber Dozen 30 inch</t>
-        </is>
-      </c>
-      <c r="AH506" t="inlineStr">
-        <is>
-          <t>1518</t>
-        </is>
-      </c>
-      <c r="AI506" t="inlineStr">
-        <is>
-          <t>JRacenstein</t>
-        </is>
-      </c>
-      <c r="AJ506" t="inlineStr">
-        <is>
-          <t>1 shared tokens, category fit</t>
-        </is>
-      </c>
+      <c r="AF506" t="inlineStr"/>
+      <c r="AG506" t="inlineStr"/>
+      <c r="AH506" t="inlineStr"/>
+      <c r="AI506" t="inlineStr"/>
+      <c r="AJ506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -72268,7 +72408,7 @@
       </c>
       <c r="N527" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>0.463</t>
         </is>
       </c>
       <c r="O527" t="inlineStr">
@@ -72288,12 +72428,12 @@
       </c>
       <c r="V527" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>0.463</t>
         </is>
       </c>
       <c r="W527" t="inlineStr">
         <is>
-          <t>Sorbo Replacement Rubber Dozen 14 inch</t>
+          <t>T-Shaped Rubber, 14"</t>
         </is>
       </c>
       <c r="X527" t="inlineStr">
